--- a/pack/staffbook-staff-file-pack.xlsx
+++ b/pack/staffbook-staff-file-pack.xlsx
@@ -3,24 +3,28 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
     <sheet name="Start here" sheetId="1" r:id="rId1"/>
-    <sheet name="Training matrix" sheetId="2" r:id="rId2"/>
-    <sheet name="Supervision tracker" sheetId="3" r:id="rId3"/>
-    <sheet name="DBS re-check log" sheetId="4" r:id="rId4"/>
-    <sheet name="Diploma clocks" sheetId="5" r:id="rId5"/>
-    <sheet name="Governance clocks" sheetId="6" r:id="rId6"/>
-    <sheet name="Staff file checklist" sheetId="7" r:id="rId7"/>
-    <sheet name="Employment gaps" sheetId="8" r:id="rId8"/>
-    <sheet name="Inspection self-audit" sheetId="9" r:id="rId9"/>
+    <sheet name="Annex A staffing" sheetId="2" r:id="rId2"/>
+    <sheet name="Staff list" sheetId="3" r:id="rId3"/>
+    <sheet name="Agency shifts" sheetId="4" r:id="rId4"/>
+    <sheet name="Training matrix" sheetId="5" r:id="rId5"/>
+    <sheet name="Supervision tracker" sheetId="6" r:id="rId6"/>
+    <sheet name="DBS re-check log" sheetId="7" r:id="rId7"/>
+    <sheet name="Governance clocks" sheetId="8" r:id="rId8"/>
+    <sheet name="Staff file checklist" sheetId="9" r:id="rId9"/>
+    <sheet name="Employment gaps" sheetId="10" r:id="rId10"/>
+    <sheet name="Inspection self-audit" sheetId="11" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Training matrix'!$4:$5</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Supervision tracker'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">'DBS re-check log'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Diploma clocks'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Governance clocks'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Staff file checklist'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="7">'Employment gaps'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="8">'Inspection self-audit'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Annex A staffing'!$12:$12</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Staff list'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Agency shifts'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Training matrix'!$4:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Supervision tracker'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'DBS re-check log'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="7">'Governance clocks'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="8">'Staff file checklist'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="9">'Employment gaps'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="10">'Inspection self-audit'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -119,21 +123,21 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -196,7 +200,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>One minute, then you know the whole pack.</t>
+          <t>One minute, then you know the whole pack. Made by Staffbook. Free to keep, copy and share.</t>
         </is>
       </c>
     </row>
@@ -212,109 +216,133 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Training matrix</t>
+          <t>Annex A staffing</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Type each person's name, then the date they did each course under "Done on". The tinted cell beside it fills in the expiry. In Excel and Google Sheets it also turns green, amber or red.</t>
+          <t>The staffing numbers Ofsted asks for on notice of a full inspection (Section 7 of Annex A), answered from your staff list and agency log. Fill those two tabs and this one fills itself.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Supervision tracker</t>
+          <t>Staff list</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Name, your cycle in days, date of the last supervision. It flags OVERDUE by itself. Put the manager on the list too.</t>
+          <t>One row per person, leavers included. Start date, contract, hours, level 3 dates, first aid. The regulation 32 status works itself out.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>DBS re-check log</t>
+          <t>Agency shifts</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>For staff on the Update Service: note each status check and it works out when the next one is due.</t>
+          <t>One line per agency shift. Ofsted counts the shifts and the different people; so does this.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Diploma clocks</t>
+          <t>Training matrix</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Start date plus whether they hold the Level 3. The two-year deadline computes itself.</t>
+          <t>Type each person's name, then the date they did each course under "Done on". The tinted cell beside it fills in the expiry. In Excel and Google Sheets it also turns green, amber or red.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Governance clocks</t>
+          <t>Supervision tracker</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Date each document was last reviewed; next-due dates compute. The monthly visit grid lives here too.</t>
+          <t>Name, your cycle in days, date of the last supervision. It flags OVERDUE by itself. Put the manager on the list too.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Staff file checklist</t>
+          <t>DBS re-check log</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>One copy of this tab per person. It is the exact list an inspector reads a file against.</t>
+          <t>For staff on the Update Service: note each status check and it works out when the next one is due.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Employment gaps</t>
+          <t>Governance clocks</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>The most common file failure. Work backwards from their current job; every gap over a month gets one written sentence.</t>
+          <t>Date each document was last reviewed; next-due dates compute. The monthly visit grid lives here too.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
+          <t>Staff file checklist</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>One copy of this tab per person. It is the exact list an inspector reads a file against.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Employment gaps</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>The most common file failure. Work backwards from their current job; every gap over a month gets one written sentence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
           <t>Inspection self-audit</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>The eleven things every inspection opens with. Grade yourself honestly.</t>
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>Each tab has an example row you can overtype or delete.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>staffbook.co.uk</t>
         </is>
@@ -325,15 +353,3231 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="FF0D5C45"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="36" customWidth="1"/>
+    <col min="4" max="4" width="24" customWidth="1"/>
+    <col min="5" max="5" width="26" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Employment history, gaps explained</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Work backwards from their current job. The most common file failure is a gap with no written explanation. "Travelling" written down is a pass. Silence is a finding.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>From (month/year)</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>To (month/year)</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Employer, course, or what the gap was</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Reason for leaving</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Checked?</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="7"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="7"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="7"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="7"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="7"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="7"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="7"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="7"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="7"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="7"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="7"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="7"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="7"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="7"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="7"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="7"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="7"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="7"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="7"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:F2"/>
+  </mergeCells>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="FF0D5C45"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="46" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="40" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>The inspector's opening list</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>The eleven staff-side things every full inspection asks for. Grade yourself honestly before Ofsted does it for you.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>The inspector asks for</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Where yours lives today</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Ready / Question / Gap</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>What would make it Ready</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Statement of purpose, current and reviewed</t>
+        </is>
+      </c>
+      <c r="B5" s="5"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="5"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Staff list with qualifications and planned qualification updates</t>
+        </is>
+      </c>
+      <c r="B6" s="5"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="5"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Recruitment and vetting records, complete for every person</t>
+        </is>
+      </c>
+      <c r="B7" s="5"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="5"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Training records, mandatory courses in date</t>
+        </is>
+      </c>
+      <c r="B8" s="5"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Supervision records, everyone in cycle including the manager</t>
+        </is>
+      </c>
+      <c r="B9" s="5"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="5"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Staffing rotas, planned and as actually worked</t>
+        </is>
+      </c>
+      <c r="B10" s="5"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="5"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Allegations records, held securely with timescales evidenced</t>
+        </is>
+      </c>
+      <c r="B11" s="5"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="5"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Reports of monthly regulation 44 visits</t>
+        </is>
+      </c>
+      <c r="B12" s="5"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="5"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Regulation 45 quality of care report, within six months</t>
+        </is>
+      </c>
+      <c r="B13" s="5"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="5"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Notifications made to Ofsted, with who else was told</t>
+        </is>
+      </c>
+      <c r="B14" s="5"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="5"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Location assessment, reviewed within the year</t>
+        </is>
+      </c>
+      <c r="B15" s="5"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="FF0D5C45"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="7" customWidth="1"/>
+    <col min="2" max="2" width="70" customWidth="1"/>
+    <col min="3" max="3" width="28" customWidth="1"/>
+    <col min="4" max="4" width="44" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Annex A, the staffing answers</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Ofsted's request for information at a full inspection of a children's home (Section 7, staffing; form updated 1 April 2026). Fill the Staff list and Agency shifts tabs and these answer themselves. The numbers are the form's at the time of writing; check the wording against the copy Ofsted sends you.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Your answers</t>
+        </is>
+      </c>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5"/>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Date of the last full inspection</t>
+        </is>
+      </c>
+      <c r="C5" s="7"/>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>Everything "since the last full inspection" counts from this date</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5"/>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Care staff vacancies today</t>
+        </is>
+      </c>
+      <c r="C6" s="7"/>
+      <c r="D6" s="5"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5"/>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Registered manager holds the level 5 diploma or equivalent (Yes/No)</t>
+        </is>
+      </c>
+      <c r="C7" s="7"/>
+      <c r="D7" s="5"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5"/>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Registered manager holds a level 4 diploma or equivalent (Yes/No)</t>
+        </is>
+      </c>
+      <c r="C8" s="7"/>
+      <c r="D8" s="5"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>If both are No: the qualification held, or "post vacant"</t>
+        </is>
+      </c>
+      <c r="C9" s="7"/>
+      <c r="D9" s="5"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5"/>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Staff trained on children's healthcare needs since the last inspection (Yes/No)</t>
+        </is>
+      </c>
+      <c r="C10" s="7"/>
+      <c r="D10" s="5"/>
+    </row>
+    <row r="11"/>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>The form asks</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Answer (auto)</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Where it comes from</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>28.1</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Does the registered manager hold the level 5 diploma or equivalent?</t>
+        </is>
+      </c>
+      <c r="C13" s="9">
+        <f>IF(C7="","",C7)</f>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>Your answer above</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>28.2</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Does the registered manager hold a level 4 diploma or equivalent?</t>
+        </is>
+      </c>
+      <c r="C14" s="9">
+        <f>IF(C8="","",C8)</f>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>Your answer above</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>28.3</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>If both are no, the qualification held, or "post vacant"</t>
+        </is>
+      </c>
+      <c r="C15" s="9">
+        <f>IF(C9="","",C9)</f>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>Your answer above</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>29.1</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Number of new staff in a care role since the last full inspection</t>
+        </is>
+      </c>
+      <c r="C16" s="9">
+        <f>IF($C$5="","",COUNTIFS('Staff list'!$B$6:$B$45,"Yes",'Staff list'!$E$6:$E$45,"&gt;"&amp;$C$5))</f>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>Staff list: care role, start date after the inspection date</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>29.2</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Number of staff in a care role who have left since the last full inspection</t>
+        </is>
+      </c>
+      <c r="C17" s="9">
+        <f>IF($C$5="","",COUNTIFS('Staff list'!$B$6:$B$45,"Yes",'Staff list'!$F$6:$F$45,"&gt;"&amp;$C$5))</f>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>Staff list: care role, left on after the inspection date</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>30.1</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>How many times have agency or other non-permanent staff been used in a care role since the last full inspection?</t>
+        </is>
+      </c>
+      <c r="C18" s="9">
+        <f>IF($C$5="","",COUNTIFS('Agency shifts'!$A$6:$A$205,"&gt;"&amp;$C$5))</f>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>Agency shifts: lines dated after the inspection date</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>30.2</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>How many different members of agency or other non-permanent staff have been used in a care role since the last full inspection?</t>
+        </is>
+      </c>
+      <c r="C19" s="9">
+        <f>IF($C$5="","",SUMPRODUCT((('Agency shifts'!$A$6:$A$205&gt;$C$5)*('Agency shifts'!$B$6:$B$205&lt;&gt;""))/(COUNTIFS('Agency shifts'!$B$6:$B$205,'Agency shifts'!$B$6:$B$205&amp;"",'Agency shifts'!$A$6:$A$205,"&gt;"&amp;$C$5)+('Agency shifts'!$A$6:$A$205&lt;=$C$5)+('Agency shifts'!$B$6:$B$205=""))))</f>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>Agency shifts: different names after the inspection date</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>31.1</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Number of permanent staff in a care role (people)</t>
+        </is>
+      </c>
+      <c r="C20" s="9">
+        <f>COUNTIFS('Staff list'!$B$6:$B$45,"Yes",'Staff list'!$F$6:$F$45,"",'Staff list'!$C$6:$C$45,"Permanent")</f>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>Staff list: care role, permanent, not left</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>31.2</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>How many of these permanent staff in a care role work part time only?</t>
+        </is>
+      </c>
+      <c r="C21" s="9">
+        <f>COUNTIFS('Staff list'!$B$6:$B$45,"Yes",'Staff list'!$F$6:$F$45,"",'Staff list'!$C$6:$C$45,"Permanent",'Staff list'!$D$6:$D$45,"Part time")</f>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>Staff list: as above, part time</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>32.1</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Number of agency/other (non-permanent) staff in a care role (people)</t>
+        </is>
+      </c>
+      <c r="C22" s="9">
+        <f>COUNTIFS('Staff list'!$B$6:$B$45,"Yes",'Staff list'!$F$6:$F$45,"",'Staff list'!$C$6:$C$45,"Agency or temporary")</f>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>Staff list: care role, agency or temporary, not left</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>32.2</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>How many of these agency/other (non-permanent) staff work in a care role part time only?</t>
+        </is>
+      </c>
+      <c r="C23" s="9">
+        <f>COUNTIFS('Staff list'!$B$6:$B$45,"Yes",'Staff list'!$F$6:$F$45,"",'Staff list'!$C$6:$C$45,"Agency or temporary",'Staff list'!$D$6:$D$45,"Part time")</f>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>Staff list: as above, part time</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Number of staff in a care role with a level 3 diploma or equivalent</t>
+        </is>
+      </c>
+      <c r="C24" s="9">
+        <f>COUNTIFS('Staff list'!$B$6:$B$45,"Yes",'Staff list'!$F$6:$F$45,"",'Staff list'!$G$6:$G$45,"&lt;&gt;")</f>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>Staff list: care role, not left, level 3 held on filled</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>34.1</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Number of staff in a care role for whom the relevant date for qualification under Regulation 32 has passed</t>
+        </is>
+      </c>
+      <c r="C25" s="9">
+        <f>COUNTIFS('Staff list'!$B$6:$B$45,"Yes",'Staff list'!$F$6:$F$45,"",'Staff list'!$D$6:$D$45,"Full time",'Staff list'!$E$6:$E$45,"&lt;="&amp;EDATE(TODAY(),-24))+COUNTIFS('Staff list'!$B$6:$B$45,"Yes",'Staff list'!$F$6:$F$45,"",'Staff list'!$D$6:$D$45,"Part time",'Staff list'!$E$6:$E$45,"&lt;="&amp;EDATE(TODAY(),-60))</f>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>Staff list: started over two years ago (five for part time, the form's own suggestion)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>34.2</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>How many of the staff in 34.1 are qualified to diploma level 3?</t>
+        </is>
+      </c>
+      <c r="C26" s="9">
+        <f>COUNTIFS('Staff list'!$B$6:$B$45,"Yes",'Staff list'!$F$6:$F$45,"",'Staff list'!$D$6:$D$45,"Full time",'Staff list'!$E$6:$E$45,"&lt;="&amp;EDATE(TODAY(),-24),'Staff list'!$G$6:$G$45,"&lt;&gt;")+COUNTIFS('Staff list'!$B$6:$B$45,"Yes",'Staff list'!$F$6:$F$45,"",'Staff list'!$D$6:$D$45,"Part time",'Staff list'!$E$6:$E$45,"&lt;="&amp;EDATE(TODAY(),-60),'Staff list'!$G$6:$G$45,"&lt;&gt;")</f>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>Staff list: as 34.1 with level 3 held on filled</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>34.3</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>How many of the staff in 34.1 are undertaking the diploma level 3?</t>
+        </is>
+      </c>
+      <c r="C27" s="9">
+        <f>COUNTIFS('Staff list'!$B$6:$B$45,"Yes",'Staff list'!$F$6:$F$45,"",'Staff list'!$D$6:$D$45,"Full time",'Staff list'!$E$6:$E$45,"&lt;="&amp;EDATE(TODAY(),-24),'Staff list'!$G$6:$G$45,"",'Staff list'!$H$6:$H$45,"&lt;&gt;")+COUNTIFS('Staff list'!$B$6:$B$45,"Yes",'Staff list'!$F$6:$F$45,"",'Staff list'!$D$6:$D$45,"Part time",'Staff list'!$E$6:$E$45,"&lt;="&amp;EDATE(TODAY(),-60),'Staff list'!$G$6:$G$45,"",'Staff list'!$H$6:$H$45,"&lt;&gt;")</f>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>Staff list: as 34.1, started but not held</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>34.4</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Names and expected qualification dates of staff in 34.3</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>See the Staff list: rows whose Status reads "Date passed, undertaking", with the date in Level 3 expected</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>Staff list, Status column</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Number of all staff with a valid first aid qualification</t>
+        </is>
+      </c>
+      <c r="C29" s="9">
+        <f>COUNTIFS('Staff list'!$F$6:$F$45,"",'Staff list'!$J$6:$J$45,"&gt;="&amp;TODAY())</f>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>Staff list: not left, first aid valid until today or later</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>How many staff vacancies (for staff in a care role) do you currently have?</t>
+        </is>
+      </c>
+      <c r="C30" s="9">
+        <f>IF(C6="","",C6)</f>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>Your answer above</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Have staff received specific training since the last inspection in relation to children's healthcare needs?</t>
+        </is>
+      </c>
+      <c r="C31" s="9">
+        <f>IF(C10="","",C10)</f>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>Your answer above</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7"/>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Date the statement of purpose was last updated</t>
+        </is>
+      </c>
+      <c r="C32" s="10">
+        <f>IF('Governance clocks'!B5="","",'Governance clocks'!B5)</f>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>Governance clocks, row 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7"/>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Date of the last annual assessment of the location of the home</t>
+        </is>
+      </c>
+      <c r="C33" s="10">
+        <f>IF('Governance clocks'!B6="","",'Governance clocks'!B6)</f>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>Governance clocks, row 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="34"/>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>Regulation 32: care staff complete the level 3 diploma within two years of starting (the form suggests five years for part time). Regulation 28: the registered manager completes the level 5 within three years.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="A35:D35"/>
+  </mergeCells>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="FF0D5C45"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="13" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="13" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+    <col min="11" max="11" width="20" customWidth="1"/>
+    <col min="12" max="12" width="26" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Staff list</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>One row per person, leavers included (put the date they left in column F; they stay for the counts). Care role means they work directly with the children. The Status column works itself out from regulation 32: the level 3 within two years of starting, five years for part time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4" ht="44" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Staff member</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Care role? (Yes/No)</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Contract (Permanent / Agency or temporary)</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Hours (Full time / Part time)</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Start date</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Left on</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Level 3 held on</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Level 3 started on</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>Level 3 expected</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>First aid valid until</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>Regulation 32 status (auto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Type in the white cells. Yes/No, Permanent/Agency or temporary and Full time/Part time must be spelled that way for the counts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Example, overtype or delete me</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>Full time</t>
+        </is>
+      </c>
+      <c r="E6" s="11">
+        <v>45371</v>
+      </c>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="11">
+        <v>45971</v>
+      </c>
+      <c r="I6" s="11">
+        <v>46391</v>
+      </c>
+      <c r="J6" s="11">
+        <v>46471</v>
+      </c>
+      <c r="K6" s="5"/>
+      <c r="L6" s="9">
+        <f>IF(OR(B6&lt;&gt;"Yes",F6&lt;&gt;""),"",IF(G6&lt;&gt;"","Qualified",IF(E6="","",IF(E6&lt;=EDATE(TODAY(),IF(D6="Part time",-60,-24)),IF(H6&lt;&gt;"","Date passed, undertaking","Date passed, not started"),IF(H6&lt;&gt;"","Undertaking, in time","Due by "&amp;TEXT(EDATE(E6,24),"dd/mm/yyyy"))))))</f>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="5"/>
+      <c r="L7" s="9">
+        <f>IF(OR(B7&lt;&gt;"Yes",F7&lt;&gt;""),"",IF(G7&lt;&gt;"","Qualified",IF(E7="","",IF(E7&lt;=EDATE(TODAY(),IF(D7="Part time",-60,-24)),IF(H7&lt;&gt;"","Date passed, undertaking","Date passed, not started"),IF(H7&lt;&gt;"","Undertaking, in time","Due by "&amp;TEXT(EDATE(E7,24),"dd/mm/yyyy"))))))</f>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="9">
+        <f>IF(OR(B8&lt;&gt;"Yes",F8&lt;&gt;""),"",IF(G8&lt;&gt;"","Qualified",IF(E8="","",IF(E8&lt;=EDATE(TODAY(),IF(D8="Part time",-60,-24)),IF(H8&lt;&gt;"","Date passed, undertaking","Date passed, not started"),IF(H8&lt;&gt;"","Undertaking, in time","Due by "&amp;TEXT(EDATE(E8,24),"dd/mm/yyyy"))))))</f>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="5"/>
+      <c r="L9" s="9">
+        <f>IF(OR(B9&lt;&gt;"Yes",F9&lt;&gt;""),"",IF(G9&lt;&gt;"","Qualified",IF(E9="","",IF(E9&lt;=EDATE(TODAY(),IF(D9="Part time",-60,-24)),IF(H9&lt;&gt;"","Date passed, undertaking","Date passed, not started"),IF(H9&lt;&gt;"","Undertaking, in time","Due by "&amp;TEXT(EDATE(E9,24),"dd/mm/yyyy"))))))</f>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="9">
+        <f>IF(OR(B10&lt;&gt;"Yes",F10&lt;&gt;""),"",IF(G10&lt;&gt;"","Qualified",IF(E10="","",IF(E10&lt;=EDATE(TODAY(),IF(D10="Part time",-60,-24)),IF(H10&lt;&gt;"","Date passed, undertaking","Date passed, not started"),IF(H10&lt;&gt;"","Undertaking, in time","Due by "&amp;TEXT(EDATE(E10,24),"dd/mm/yyyy"))))))</f>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="5"/>
+      <c r="L11" s="9">
+        <f>IF(OR(B11&lt;&gt;"Yes",F11&lt;&gt;""),"",IF(G11&lt;&gt;"","Qualified",IF(E11="","",IF(E11&lt;=EDATE(TODAY(),IF(D11="Part time",-60,-24)),IF(H11&lt;&gt;"","Date passed, undertaking","Date passed, not started"),IF(H11&lt;&gt;"","Undertaking, in time","Due by "&amp;TEXT(EDATE(E11,24),"dd/mm/yyyy"))))))</f>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="5"/>
+      <c r="L12" s="9">
+        <f>IF(OR(B12&lt;&gt;"Yes",F12&lt;&gt;""),"",IF(G12&lt;&gt;"","Qualified",IF(E12="","",IF(E12&lt;=EDATE(TODAY(),IF(D12="Part time",-60,-24)),IF(H12&lt;&gt;"","Date passed, undertaking","Date passed, not started"),IF(H12&lt;&gt;"","Undertaking, in time","Due by "&amp;TEXT(EDATE(E12,24),"dd/mm/yyyy"))))))</f>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="5"/>
+      <c r="L13" s="9">
+        <f>IF(OR(B13&lt;&gt;"Yes",F13&lt;&gt;""),"",IF(G13&lt;&gt;"","Qualified",IF(E13="","",IF(E13&lt;=EDATE(TODAY(),IF(D13="Part time",-60,-24)),IF(H13&lt;&gt;"","Date passed, undertaking","Date passed, not started"),IF(H13&lt;&gt;"","Undertaking, in time","Due by "&amp;TEXT(EDATE(E13,24),"dd/mm/yyyy"))))))</f>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="9">
+        <f>IF(OR(B14&lt;&gt;"Yes",F14&lt;&gt;""),"",IF(G14&lt;&gt;"","Qualified",IF(E14="","",IF(E14&lt;=EDATE(TODAY(),IF(D14="Part time",-60,-24)),IF(H14&lt;&gt;"","Date passed, undertaking","Date passed, not started"),IF(H14&lt;&gt;"","Undertaking, in time","Due by "&amp;TEXT(EDATE(E14,24),"dd/mm/yyyy"))))))</f>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="5"/>
+      <c r="L15" s="9">
+        <f>IF(OR(B15&lt;&gt;"Yes",F15&lt;&gt;""),"",IF(G15&lt;&gt;"","Qualified",IF(E15="","",IF(E15&lt;=EDATE(TODAY(),IF(D15="Part time",-60,-24)),IF(H15&lt;&gt;"","Date passed, undertaking","Date passed, not started"),IF(H15&lt;&gt;"","Undertaking, in time","Due by "&amp;TEXT(EDATE(E15,24),"dd/mm/yyyy"))))))</f>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="7"/>
+      <c r="J16" s="7"/>
+      <c r="K16" s="5"/>
+      <c r="L16" s="9">
+        <f>IF(OR(B16&lt;&gt;"Yes",F16&lt;&gt;""),"",IF(G16&lt;&gt;"","Qualified",IF(E16="","",IF(E16&lt;=EDATE(TODAY(),IF(D16="Part time",-60,-24)),IF(H16&lt;&gt;"","Date passed, undertaking","Date passed, not started"),IF(H16&lt;&gt;"","Undertaking, in time","Due by "&amp;TEXT(EDATE(E16,24),"dd/mm/yyyy"))))))</f>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="7"/>
+      <c r="K17" s="5"/>
+      <c r="L17" s="9">
+        <f>IF(OR(B17&lt;&gt;"Yes",F17&lt;&gt;""),"",IF(G17&lt;&gt;"","Qualified",IF(E17="","",IF(E17&lt;=EDATE(TODAY(),IF(D17="Part time",-60,-24)),IF(H17&lt;&gt;"","Date passed, undertaking","Date passed, not started"),IF(H17&lt;&gt;"","Undertaking, in time","Due by "&amp;TEXT(EDATE(E17,24),"dd/mm/yyyy"))))))</f>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="7"/>
+      <c r="K18" s="5"/>
+      <c r="L18" s="9">
+        <f>IF(OR(B18&lt;&gt;"Yes",F18&lt;&gt;""),"",IF(G18&lt;&gt;"","Qualified",IF(E18="","",IF(E18&lt;=EDATE(TODAY(),IF(D18="Part time",-60,-24)),IF(H18&lt;&gt;"","Date passed, undertaking","Date passed, not started"),IF(H18&lt;&gt;"","Undertaking, in time","Due by "&amp;TEXT(EDATE(E18,24),"dd/mm/yyyy"))))))</f>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="7"/>
+      <c r="J19" s="7"/>
+      <c r="K19" s="5"/>
+      <c r="L19" s="9">
+        <f>IF(OR(B19&lt;&gt;"Yes",F19&lt;&gt;""),"",IF(G19&lt;&gt;"","Qualified",IF(E19="","",IF(E19&lt;=EDATE(TODAY(),IF(D19="Part time",-60,-24)),IF(H19&lt;&gt;"","Date passed, undertaking","Date passed, not started"),IF(H19&lt;&gt;"","Undertaking, in time","Due by "&amp;TEXT(EDATE(E19,24),"dd/mm/yyyy"))))))</f>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7"/>
+      <c r="I20" s="7"/>
+      <c r="J20" s="7"/>
+      <c r="K20" s="5"/>
+      <c r="L20" s="9">
+        <f>IF(OR(B20&lt;&gt;"Yes",F20&lt;&gt;""),"",IF(G20&lt;&gt;"","Qualified",IF(E20="","",IF(E20&lt;=EDATE(TODAY(),IF(D20="Part time",-60,-24)),IF(H20&lt;&gt;"","Date passed, undertaking","Date passed, not started"),IF(H20&lt;&gt;"","Undertaking, in time","Due by "&amp;TEXT(EDATE(E20,24),"dd/mm/yyyy"))))))</f>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="7"/>
+      <c r="I21" s="7"/>
+      <c r="J21" s="7"/>
+      <c r="K21" s="5"/>
+      <c r="L21" s="9">
+        <f>IF(OR(B21&lt;&gt;"Yes",F21&lt;&gt;""),"",IF(G21&lt;&gt;"","Qualified",IF(E21="","",IF(E21&lt;=EDATE(TODAY(),IF(D21="Part time",-60,-24)),IF(H21&lt;&gt;"","Date passed, undertaking","Date passed, not started"),IF(H21&lt;&gt;"","Undertaking, in time","Due by "&amp;TEXT(EDATE(E21,24),"dd/mm/yyyy"))))))</f>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7"/>
+      <c r="I22" s="7"/>
+      <c r="J22" s="7"/>
+      <c r="K22" s="5"/>
+      <c r="L22" s="9">
+        <f>IF(OR(B22&lt;&gt;"Yes",F22&lt;&gt;""),"",IF(G22&lt;&gt;"","Qualified",IF(E22="","",IF(E22&lt;=EDATE(TODAY(),IF(D22="Part time",-60,-24)),IF(H22&lt;&gt;"","Date passed, undertaking","Date passed, not started"),IF(H22&lt;&gt;"","Undertaking, in time","Due by "&amp;TEXT(EDATE(E22,24),"dd/mm/yyyy"))))))</f>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="7"/>
+      <c r="I23" s="7"/>
+      <c r="J23" s="7"/>
+      <c r="K23" s="5"/>
+      <c r="L23" s="9">
+        <f>IF(OR(B23&lt;&gt;"Yes",F23&lt;&gt;""),"",IF(G23&lt;&gt;"","Qualified",IF(E23="","",IF(E23&lt;=EDATE(TODAY(),IF(D23="Part time",-60,-24)),IF(H23&lt;&gt;"","Date passed, undertaking","Date passed, not started"),IF(H23&lt;&gt;"","Undertaking, in time","Due by "&amp;TEXT(EDATE(E23,24),"dd/mm/yyyy"))))))</f>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
+      <c r="H24" s="7"/>
+      <c r="I24" s="7"/>
+      <c r="J24" s="7"/>
+      <c r="K24" s="5"/>
+      <c r="L24" s="9">
+        <f>IF(OR(B24&lt;&gt;"Yes",F24&lt;&gt;""),"",IF(G24&lt;&gt;"","Qualified",IF(E24="","",IF(E24&lt;=EDATE(TODAY(),IF(D24="Part time",-60,-24)),IF(H24&lt;&gt;"","Date passed, undertaking","Date passed, not started"),IF(H24&lt;&gt;"","Undertaking, in time","Due by "&amp;TEXT(EDATE(E24,24),"dd/mm/yyyy"))))))</f>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+      <c r="H25" s="7"/>
+      <c r="I25" s="7"/>
+      <c r="J25" s="7"/>
+      <c r="K25" s="5"/>
+      <c r="L25" s="9">
+        <f>IF(OR(B25&lt;&gt;"Yes",F25&lt;&gt;""),"",IF(G25&lt;&gt;"","Qualified",IF(E25="","",IF(E25&lt;=EDATE(TODAY(),IF(D25="Part time",-60,-24)),IF(H25&lt;&gt;"","Date passed, undertaking","Date passed, not started"),IF(H25&lt;&gt;"","Undertaking, in time","Due by "&amp;TEXT(EDATE(E25,24),"dd/mm/yyyy"))))))</f>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="7"/>
+      <c r="H26" s="7"/>
+      <c r="I26" s="7"/>
+      <c r="J26" s="7"/>
+      <c r="K26" s="5"/>
+      <c r="L26" s="9">
+        <f>IF(OR(B26&lt;&gt;"Yes",F26&lt;&gt;""),"",IF(G26&lt;&gt;"","Qualified",IF(E26="","",IF(E26&lt;=EDATE(TODAY(),IF(D26="Part time",-60,-24)),IF(H26&lt;&gt;"","Date passed, undertaking","Date passed, not started"),IF(H26&lt;&gt;"","Undertaking, in time","Due by "&amp;TEXT(EDATE(E26,24),"dd/mm/yyyy"))))))</f>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5"/>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="7"/>
+      <c r="G27" s="7"/>
+      <c r="H27" s="7"/>
+      <c r="I27" s="7"/>
+      <c r="J27" s="7"/>
+      <c r="K27" s="5"/>
+      <c r="L27" s="9">
+        <f>IF(OR(B27&lt;&gt;"Yes",F27&lt;&gt;""),"",IF(G27&lt;&gt;"","Qualified",IF(E27="","",IF(E27&lt;=EDATE(TODAY(),IF(D27="Part time",-60,-24)),IF(H27&lt;&gt;"","Date passed, undertaking","Date passed, not started"),IF(H27&lt;&gt;"","Undertaking, in time","Due by "&amp;TEXT(EDATE(E27,24),"dd/mm/yyyy"))))))</f>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5"/>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="7"/>
+      <c r="H28" s="7"/>
+      <c r="I28" s="7"/>
+      <c r="J28" s="7"/>
+      <c r="K28" s="5"/>
+      <c r="L28" s="9">
+        <f>IF(OR(B28&lt;&gt;"Yes",F28&lt;&gt;""),"",IF(G28&lt;&gt;"","Qualified",IF(E28="","",IF(E28&lt;=EDATE(TODAY(),IF(D28="Part time",-60,-24)),IF(H28&lt;&gt;"","Date passed, undertaking","Date passed, not started"),IF(H28&lt;&gt;"","Undertaking, in time","Due by "&amp;TEXT(EDATE(E28,24),"dd/mm/yyyy"))))))</f>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5"/>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="7"/>
+      <c r="H29" s="7"/>
+      <c r="I29" s="7"/>
+      <c r="J29" s="7"/>
+      <c r="K29" s="5"/>
+      <c r="L29" s="9">
+        <f>IF(OR(B29&lt;&gt;"Yes",F29&lt;&gt;""),"",IF(G29&lt;&gt;"","Qualified",IF(E29="","",IF(E29&lt;=EDATE(TODAY(),IF(D29="Part time",-60,-24)),IF(H29&lt;&gt;"","Date passed, undertaking","Date passed, not started"),IF(H29&lt;&gt;"","Undertaking, in time","Due by "&amp;TEXT(EDATE(E29,24),"dd/mm/yyyy"))))))</f>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5"/>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="7"/>
+      <c r="G30" s="7"/>
+      <c r="H30" s="7"/>
+      <c r="I30" s="7"/>
+      <c r="J30" s="7"/>
+      <c r="K30" s="5"/>
+      <c r="L30" s="9">
+        <f>IF(OR(B30&lt;&gt;"Yes",F30&lt;&gt;""),"",IF(G30&lt;&gt;"","Qualified",IF(E30="","",IF(E30&lt;=EDATE(TODAY(),IF(D30="Part time",-60,-24)),IF(H30&lt;&gt;"","Date passed, undertaking","Date passed, not started"),IF(H30&lt;&gt;"","Undertaking, in time","Due by "&amp;TEXT(EDATE(E30,24),"dd/mm/yyyy"))))))</f>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5"/>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="7"/>
+      <c r="G31" s="7"/>
+      <c r="H31" s="7"/>
+      <c r="I31" s="7"/>
+      <c r="J31" s="7"/>
+      <c r="K31" s="5"/>
+      <c r="L31" s="9">
+        <f>IF(OR(B31&lt;&gt;"Yes",F31&lt;&gt;""),"",IF(G31&lt;&gt;"","Qualified",IF(E31="","",IF(E31&lt;=EDATE(TODAY(),IF(D31="Part time",-60,-24)),IF(H31&lt;&gt;"","Date passed, undertaking","Date passed, not started"),IF(H31&lt;&gt;"","Undertaking, in time","Due by "&amp;TEXT(EDATE(E31,24),"dd/mm/yyyy"))))))</f>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5"/>
+      <c r="B32" s="7"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="7"/>
+      <c r="G32" s="7"/>
+      <c r="H32" s="7"/>
+      <c r="I32" s="7"/>
+      <c r="J32" s="7"/>
+      <c r="K32" s="5"/>
+      <c r="L32" s="9">
+        <f>IF(OR(B32&lt;&gt;"Yes",F32&lt;&gt;""),"",IF(G32&lt;&gt;"","Qualified",IF(E32="","",IF(E32&lt;=EDATE(TODAY(),IF(D32="Part time",-60,-24)),IF(H32&lt;&gt;"","Date passed, undertaking","Date passed, not started"),IF(H32&lt;&gt;"","Undertaking, in time","Due by "&amp;TEXT(EDATE(E32,24),"dd/mm/yyyy"))))))</f>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5"/>
+      <c r="B33" s="7"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
+      <c r="G33" s="7"/>
+      <c r="H33" s="7"/>
+      <c r="I33" s="7"/>
+      <c r="J33" s="7"/>
+      <c r="K33" s="5"/>
+      <c r="L33" s="9">
+        <f>IF(OR(B33&lt;&gt;"Yes",F33&lt;&gt;""),"",IF(G33&lt;&gt;"","Qualified",IF(E33="","",IF(E33&lt;=EDATE(TODAY(),IF(D33="Part time",-60,-24)),IF(H33&lt;&gt;"","Date passed, undertaking","Date passed, not started"),IF(H33&lt;&gt;"","Undertaking, in time","Due by "&amp;TEXT(EDATE(E33,24),"dd/mm/yyyy"))))))</f>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5"/>
+      <c r="B34" s="7"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="7"/>
+      <c r="G34" s="7"/>
+      <c r="H34" s="7"/>
+      <c r="I34" s="7"/>
+      <c r="J34" s="7"/>
+      <c r="K34" s="5"/>
+      <c r="L34" s="9">
+        <f>IF(OR(B34&lt;&gt;"Yes",F34&lt;&gt;""),"",IF(G34&lt;&gt;"","Qualified",IF(E34="","",IF(E34&lt;=EDATE(TODAY(),IF(D34="Part time",-60,-24)),IF(H34&lt;&gt;"","Date passed, undertaking","Date passed, not started"),IF(H34&lt;&gt;"","Undertaking, in time","Due by "&amp;TEXT(EDATE(E34,24),"dd/mm/yyyy"))))))</f>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5"/>
+      <c r="B35" s="7"/>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="7"/>
+      <c r="G35" s="7"/>
+      <c r="H35" s="7"/>
+      <c r="I35" s="7"/>
+      <c r="J35" s="7"/>
+      <c r="K35" s="5"/>
+      <c r="L35" s="9">
+        <f>IF(OR(B35&lt;&gt;"Yes",F35&lt;&gt;""),"",IF(G35&lt;&gt;"","Qualified",IF(E35="","",IF(E35&lt;=EDATE(TODAY(),IF(D35="Part time",-60,-24)),IF(H35&lt;&gt;"","Date passed, undertaking","Date passed, not started"),IF(H35&lt;&gt;"","Undertaking, in time","Due by "&amp;TEXT(EDATE(E35,24),"dd/mm/yyyy"))))))</f>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5"/>
+      <c r="B36" s="7"/>
+      <c r="C36" s="7"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="7"/>
+      <c r="F36" s="7"/>
+      <c r="G36" s="7"/>
+      <c r="H36" s="7"/>
+      <c r="I36" s="7"/>
+      <c r="J36" s="7"/>
+      <c r="K36" s="5"/>
+      <c r="L36" s="9">
+        <f>IF(OR(B36&lt;&gt;"Yes",F36&lt;&gt;""),"",IF(G36&lt;&gt;"","Qualified",IF(E36="","",IF(E36&lt;=EDATE(TODAY(),IF(D36="Part time",-60,-24)),IF(H36&lt;&gt;"","Date passed, undertaking","Date passed, not started"),IF(H36&lt;&gt;"","Undertaking, in time","Due by "&amp;TEXT(EDATE(E36,24),"dd/mm/yyyy"))))))</f>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5"/>
+      <c r="B37" s="7"/>
+      <c r="C37" s="7"/>
+      <c r="D37" s="7"/>
+      <c r="E37" s="7"/>
+      <c r="F37" s="7"/>
+      <c r="G37" s="7"/>
+      <c r="H37" s="7"/>
+      <c r="I37" s="7"/>
+      <c r="J37" s="7"/>
+      <c r="K37" s="5"/>
+      <c r="L37" s="9">
+        <f>IF(OR(B37&lt;&gt;"Yes",F37&lt;&gt;""),"",IF(G37&lt;&gt;"","Qualified",IF(E37="","",IF(E37&lt;=EDATE(TODAY(),IF(D37="Part time",-60,-24)),IF(H37&lt;&gt;"","Date passed, undertaking","Date passed, not started"),IF(H37&lt;&gt;"","Undertaking, in time","Due by "&amp;TEXT(EDATE(E37,24),"dd/mm/yyyy"))))))</f>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5"/>
+      <c r="B38" s="7"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="7"/>
+      <c r="E38" s="7"/>
+      <c r="F38" s="7"/>
+      <c r="G38" s="7"/>
+      <c r="H38" s="7"/>
+      <c r="I38" s="7"/>
+      <c r="J38" s="7"/>
+      <c r="K38" s="5"/>
+      <c r="L38" s="9">
+        <f>IF(OR(B38&lt;&gt;"Yes",F38&lt;&gt;""),"",IF(G38&lt;&gt;"","Qualified",IF(E38="","",IF(E38&lt;=EDATE(TODAY(),IF(D38="Part time",-60,-24)),IF(H38&lt;&gt;"","Date passed, undertaking","Date passed, not started"),IF(H38&lt;&gt;"","Undertaking, in time","Due by "&amp;TEXT(EDATE(E38,24),"dd/mm/yyyy"))))))</f>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5"/>
+      <c r="B39" s="7"/>
+      <c r="C39" s="7"/>
+      <c r="D39" s="7"/>
+      <c r="E39" s="7"/>
+      <c r="F39" s="7"/>
+      <c r="G39" s="7"/>
+      <c r="H39" s="7"/>
+      <c r="I39" s="7"/>
+      <c r="J39" s="7"/>
+      <c r="K39" s="5"/>
+      <c r="L39" s="9">
+        <f>IF(OR(B39&lt;&gt;"Yes",F39&lt;&gt;""),"",IF(G39&lt;&gt;"","Qualified",IF(E39="","",IF(E39&lt;=EDATE(TODAY(),IF(D39="Part time",-60,-24)),IF(H39&lt;&gt;"","Date passed, undertaking","Date passed, not started"),IF(H39&lt;&gt;"","Undertaking, in time","Due by "&amp;TEXT(EDATE(E39,24),"dd/mm/yyyy"))))))</f>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5"/>
+      <c r="B40" s="7"/>
+      <c r="C40" s="7"/>
+      <c r="D40" s="7"/>
+      <c r="E40" s="7"/>
+      <c r="F40" s="7"/>
+      <c r="G40" s="7"/>
+      <c r="H40" s="7"/>
+      <c r="I40" s="7"/>
+      <c r="J40" s="7"/>
+      <c r="K40" s="5"/>
+      <c r="L40" s="9">
+        <f>IF(OR(B40&lt;&gt;"Yes",F40&lt;&gt;""),"",IF(G40&lt;&gt;"","Qualified",IF(E40="","",IF(E40&lt;=EDATE(TODAY(),IF(D40="Part time",-60,-24)),IF(H40&lt;&gt;"","Date passed, undertaking","Date passed, not started"),IF(H40&lt;&gt;"","Undertaking, in time","Due by "&amp;TEXT(EDATE(E40,24),"dd/mm/yyyy"))))))</f>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5"/>
+      <c r="B41" s="7"/>
+      <c r="C41" s="7"/>
+      <c r="D41" s="7"/>
+      <c r="E41" s="7"/>
+      <c r="F41" s="7"/>
+      <c r="G41" s="7"/>
+      <c r="H41" s="7"/>
+      <c r="I41" s="7"/>
+      <c r="J41" s="7"/>
+      <c r="K41" s="5"/>
+      <c r="L41" s="9">
+        <f>IF(OR(B41&lt;&gt;"Yes",F41&lt;&gt;""),"",IF(G41&lt;&gt;"","Qualified",IF(E41="","",IF(E41&lt;=EDATE(TODAY(),IF(D41="Part time",-60,-24)),IF(H41&lt;&gt;"","Date passed, undertaking","Date passed, not started"),IF(H41&lt;&gt;"","Undertaking, in time","Due by "&amp;TEXT(EDATE(E41,24),"dd/mm/yyyy"))))))</f>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5"/>
+      <c r="B42" s="7"/>
+      <c r="C42" s="7"/>
+      <c r="D42" s="7"/>
+      <c r="E42" s="7"/>
+      <c r="F42" s="7"/>
+      <c r="G42" s="7"/>
+      <c r="H42" s="7"/>
+      <c r="I42" s="7"/>
+      <c r="J42" s="7"/>
+      <c r="K42" s="5"/>
+      <c r="L42" s="9">
+        <f>IF(OR(B42&lt;&gt;"Yes",F42&lt;&gt;""),"",IF(G42&lt;&gt;"","Qualified",IF(E42="","",IF(E42&lt;=EDATE(TODAY(),IF(D42="Part time",-60,-24)),IF(H42&lt;&gt;"","Date passed, undertaking","Date passed, not started"),IF(H42&lt;&gt;"","Undertaking, in time","Due by "&amp;TEXT(EDATE(E42,24),"dd/mm/yyyy"))))))</f>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5"/>
+      <c r="B43" s="7"/>
+      <c r="C43" s="7"/>
+      <c r="D43" s="7"/>
+      <c r="E43" s="7"/>
+      <c r="F43" s="7"/>
+      <c r="G43" s="7"/>
+      <c r="H43" s="7"/>
+      <c r="I43" s="7"/>
+      <c r="J43" s="7"/>
+      <c r="K43" s="5"/>
+      <c r="L43" s="9">
+        <f>IF(OR(B43&lt;&gt;"Yes",F43&lt;&gt;""),"",IF(G43&lt;&gt;"","Qualified",IF(E43="","",IF(E43&lt;=EDATE(TODAY(),IF(D43="Part time",-60,-24)),IF(H43&lt;&gt;"","Date passed, undertaking","Date passed, not started"),IF(H43&lt;&gt;"","Undertaking, in time","Due by "&amp;TEXT(EDATE(E43,24),"dd/mm/yyyy"))))))</f>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5"/>
+      <c r="B44" s="7"/>
+      <c r="C44" s="7"/>
+      <c r="D44" s="7"/>
+      <c r="E44" s="7"/>
+      <c r="F44" s="7"/>
+      <c r="G44" s="7"/>
+      <c r="H44" s="7"/>
+      <c r="I44" s="7"/>
+      <c r="J44" s="7"/>
+      <c r="K44" s="5"/>
+      <c r="L44" s="9">
+        <f>IF(OR(B44&lt;&gt;"Yes",F44&lt;&gt;""),"",IF(G44&lt;&gt;"","Qualified",IF(E44="","",IF(E44&lt;=EDATE(TODAY(),IF(D44="Part time",-60,-24)),IF(H44&lt;&gt;"","Date passed, undertaking","Date passed, not started"),IF(H44&lt;&gt;"","Undertaking, in time","Due by "&amp;TEXT(EDATE(E44,24),"dd/mm/yyyy"))))))</f>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5"/>
+      <c r="B45" s="7"/>
+      <c r="C45" s="7"/>
+      <c r="D45" s="7"/>
+      <c r="E45" s="7"/>
+      <c r="F45" s="7"/>
+      <c r="G45" s="7"/>
+      <c r="H45" s="7"/>
+      <c r="I45" s="7"/>
+      <c r="J45" s="7"/>
+      <c r="K45" s="5"/>
+      <c r="L45" s="9">
+        <f>IF(OR(B45&lt;&gt;"Yes",F45&lt;&gt;""),"",IF(G45&lt;&gt;"","Qualified",IF(E45="","",IF(E45&lt;=EDATE(TODAY(),IF(D45="Part time",-60,-24)),IF(H45&lt;&gt;"","Date passed, undertaking","Date passed, not started"),IF(H45&lt;&gt;"","Undertaking, in time","Due by "&amp;TEXT(EDATE(E45,24),"dd/mm/yyyy"))))))</f>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A5:L5"/>
+  </mergeCells>
+  <conditionalFormatting sqref="J6:J45">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>AND(J6&lt;&gt;"",J6&lt;TODAY())</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>AND(J6&lt;&gt;"",J6&lt;TODAY()+60)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="3">
+      <formula>AND(J6&lt;&gt;"",J6&gt;=TODAY()+60)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L6:L45">
+    <cfRule type="expression" dxfId="0" priority="4">
+      <formula>L6="Date passed, not started"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="5">
+      <formula>L6="Date passed, undertaking"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="6">
+      <formula>L6="Qualified"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="FF0D5C45"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Agency shifts</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>One line each time an agency or other non-permanent person covers a care shift. Ofsted asks for the number of times and the number of different people since the last full inspection; both count themselves on the Annex A tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Person</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Agency</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Shift</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Spell a person's name the same way each time; the count of different people relies on it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11">
+        <v>46251</v>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Example, overtype or delete me</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Agency name</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Night</t>
+        </is>
+      </c>
+      <c r="E6" s="5"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="7"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="7"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="7"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="7"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="7"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="7"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="7"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="7"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="7"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="7"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="7"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="7"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="7"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="7"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="7"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="7"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="7"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="7"/>
+      <c r="B24" s="5"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="7"/>
+      <c r="B25" s="5"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="7"/>
+      <c r="B26" s="5"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="7"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="7"/>
+      <c r="B28" s="5"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="7"/>
+      <c r="B29" s="5"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="5"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="7"/>
+      <c r="B30" s="5"/>
+      <c r="C30" s="5"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="5"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="7"/>
+      <c r="B31" s="5"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="5"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="7"/>
+      <c r="B32" s="5"/>
+      <c r="C32" s="5"/>
+      <c r="D32" s="5"/>
+      <c r="E32" s="5"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="7"/>
+      <c r="B33" s="5"/>
+      <c r="C33" s="5"/>
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="7"/>
+      <c r="B34" s="5"/>
+      <c r="C34" s="5"/>
+      <c r="D34" s="5"/>
+      <c r="E34" s="5"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="7"/>
+      <c r="B35" s="5"/>
+      <c r="C35" s="5"/>
+      <c r="D35" s="5"/>
+      <c r="E35" s="5"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="7"/>
+      <c r="B36" s="5"/>
+      <c r="C36" s="5"/>
+      <c r="D36" s="5"/>
+      <c r="E36" s="5"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="7"/>
+      <c r="B37" s="5"/>
+      <c r="C37" s="5"/>
+      <c r="D37" s="5"/>
+      <c r="E37" s="5"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="7"/>
+      <c r="B38" s="5"/>
+      <c r="C38" s="5"/>
+      <c r="D38" s="5"/>
+      <c r="E38" s="5"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="7"/>
+      <c r="B39" s="5"/>
+      <c r="C39" s="5"/>
+      <c r="D39" s="5"/>
+      <c r="E39" s="5"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="7"/>
+      <c r="B40" s="5"/>
+      <c r="C40" s="5"/>
+      <c r="D40" s="5"/>
+      <c r="E40" s="5"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="7"/>
+      <c r="B41" s="5"/>
+      <c r="C41" s="5"/>
+      <c r="D41" s="5"/>
+      <c r="E41" s="5"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="7"/>
+      <c r="B42" s="5"/>
+      <c r="C42" s="5"/>
+      <c r="D42" s="5"/>
+      <c r="E42" s="5"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="7"/>
+      <c r="B43" s="5"/>
+      <c r="C43" s="5"/>
+      <c r="D43" s="5"/>
+      <c r="E43" s="5"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="7"/>
+      <c r="B44" s="5"/>
+      <c r="C44" s="5"/>
+      <c r="D44" s="5"/>
+      <c r="E44" s="5"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="7"/>
+      <c r="B45" s="5"/>
+      <c r="C45" s="5"/>
+      <c r="D45" s="5"/>
+      <c r="E45" s="5"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="7"/>
+      <c r="B46" s="5"/>
+      <c r="C46" s="5"/>
+      <c r="D46" s="5"/>
+      <c r="E46" s="5"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="7"/>
+      <c r="B47" s="5"/>
+      <c r="C47" s="5"/>
+      <c r="D47" s="5"/>
+      <c r="E47" s="5"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="7"/>
+      <c r="B48" s="5"/>
+      <c r="C48" s="5"/>
+      <c r="D48" s="5"/>
+      <c r="E48" s="5"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="7"/>
+      <c r="B49" s="5"/>
+      <c r="C49" s="5"/>
+      <c r="D49" s="5"/>
+      <c r="E49" s="5"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="7"/>
+      <c r="B50" s="5"/>
+      <c r="C50" s="5"/>
+      <c r="D50" s="5"/>
+      <c r="E50" s="5"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="7"/>
+      <c r="B51" s="5"/>
+      <c r="C51" s="5"/>
+      <c r="D51" s="5"/>
+      <c r="E51" s="5"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="7"/>
+      <c r="B52" s="5"/>
+      <c r="C52" s="5"/>
+      <c r="D52" s="5"/>
+      <c r="E52" s="5"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="7"/>
+      <c r="B53" s="5"/>
+      <c r="C53" s="5"/>
+      <c r="D53" s="5"/>
+      <c r="E53" s="5"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="7"/>
+      <c r="B54" s="5"/>
+      <c r="C54" s="5"/>
+      <c r="D54" s="5"/>
+      <c r="E54" s="5"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="7"/>
+      <c r="B55" s="5"/>
+      <c r="C55" s="5"/>
+      <c r="D55" s="5"/>
+      <c r="E55" s="5"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="7"/>
+      <c r="B56" s="5"/>
+      <c r="C56" s="5"/>
+      <c r="D56" s="5"/>
+      <c r="E56" s="5"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="7"/>
+      <c r="B57" s="5"/>
+      <c r="C57" s="5"/>
+      <c r="D57" s="5"/>
+      <c r="E57" s="5"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="7"/>
+      <c r="B58" s="5"/>
+      <c r="C58" s="5"/>
+      <c r="D58" s="5"/>
+      <c r="E58" s="5"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="7"/>
+      <c r="B59" s="5"/>
+      <c r="C59" s="5"/>
+      <c r="D59" s="5"/>
+      <c r="E59" s="5"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="7"/>
+      <c r="B60" s="5"/>
+      <c r="C60" s="5"/>
+      <c r="D60" s="5"/>
+      <c r="E60" s="5"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="7"/>
+      <c r="B61" s="5"/>
+      <c r="C61" s="5"/>
+      <c r="D61" s="5"/>
+      <c r="E61" s="5"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="7"/>
+      <c r="B62" s="5"/>
+      <c r="C62" s="5"/>
+      <c r="D62" s="5"/>
+      <c r="E62" s="5"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="7"/>
+      <c r="B63" s="5"/>
+      <c r="C63" s="5"/>
+      <c r="D63" s="5"/>
+      <c r="E63" s="5"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="7"/>
+      <c r="B64" s="5"/>
+      <c r="C64" s="5"/>
+      <c r="D64" s="5"/>
+      <c r="E64" s="5"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="7"/>
+      <c r="B65" s="5"/>
+      <c r="C65" s="5"/>
+      <c r="D65" s="5"/>
+      <c r="E65" s="5"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="7"/>
+      <c r="B66" s="5"/>
+      <c r="C66" s="5"/>
+      <c r="D66" s="5"/>
+      <c r="E66" s="5"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="7"/>
+      <c r="B67" s="5"/>
+      <c r="C67" s="5"/>
+      <c r="D67" s="5"/>
+      <c r="E67" s="5"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="7"/>
+      <c r="B68" s="5"/>
+      <c r="C68" s="5"/>
+      <c r="D68" s="5"/>
+      <c r="E68" s="5"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="7"/>
+      <c r="B69" s="5"/>
+      <c r="C69" s="5"/>
+      <c r="D69" s="5"/>
+      <c r="E69" s="5"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="7"/>
+      <c r="B70" s="5"/>
+      <c r="C70" s="5"/>
+      <c r="D70" s="5"/>
+      <c r="E70" s="5"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="7"/>
+      <c r="B71" s="5"/>
+      <c r="C71" s="5"/>
+      <c r="D71" s="5"/>
+      <c r="E71" s="5"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="7"/>
+      <c r="B72" s="5"/>
+      <c r="C72" s="5"/>
+      <c r="D72" s="5"/>
+      <c r="E72" s="5"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="7"/>
+      <c r="B73" s="5"/>
+      <c r="C73" s="5"/>
+      <c r="D73" s="5"/>
+      <c r="E73" s="5"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="7"/>
+      <c r="B74" s="5"/>
+      <c r="C74" s="5"/>
+      <c r="D74" s="5"/>
+      <c r="E74" s="5"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="7"/>
+      <c r="B75" s="5"/>
+      <c r="C75" s="5"/>
+      <c r="D75" s="5"/>
+      <c r="E75" s="5"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="7"/>
+      <c r="B76" s="5"/>
+      <c r="C76" s="5"/>
+      <c r="D76" s="5"/>
+      <c r="E76" s="5"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="7"/>
+      <c r="B77" s="5"/>
+      <c r="C77" s="5"/>
+      <c r="D77" s="5"/>
+      <c r="E77" s="5"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="7"/>
+      <c r="B78" s="5"/>
+      <c r="C78" s="5"/>
+      <c r="D78" s="5"/>
+      <c r="E78" s="5"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="7"/>
+      <c r="B79" s="5"/>
+      <c r="C79" s="5"/>
+      <c r="D79" s="5"/>
+      <c r="E79" s="5"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="7"/>
+      <c r="B80" s="5"/>
+      <c r="C80" s="5"/>
+      <c r="D80" s="5"/>
+      <c r="E80" s="5"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="7"/>
+      <c r="B81" s="5"/>
+      <c r="C81" s="5"/>
+      <c r="D81" s="5"/>
+      <c r="E81" s="5"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="7"/>
+      <c r="B82" s="5"/>
+      <c r="C82" s="5"/>
+      <c r="D82" s="5"/>
+      <c r="E82" s="5"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="7"/>
+      <c r="B83" s="5"/>
+      <c r="C83" s="5"/>
+      <c r="D83" s="5"/>
+      <c r="E83" s="5"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="7"/>
+      <c r="B84" s="5"/>
+      <c r="C84" s="5"/>
+      <c r="D84" s="5"/>
+      <c r="E84" s="5"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="7"/>
+      <c r="B85" s="5"/>
+      <c r="C85" s="5"/>
+      <c r="D85" s="5"/>
+      <c r="E85" s="5"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="7"/>
+      <c r="B86" s="5"/>
+      <c r="C86" s="5"/>
+      <c r="D86" s="5"/>
+      <c r="E86" s="5"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="7"/>
+      <c r="B87" s="5"/>
+      <c r="C87" s="5"/>
+      <c r="D87" s="5"/>
+      <c r="E87" s="5"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="7"/>
+      <c r="B88" s="5"/>
+      <c r="C88" s="5"/>
+      <c r="D88" s="5"/>
+      <c r="E88" s="5"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="7"/>
+      <c r="B89" s="5"/>
+      <c r="C89" s="5"/>
+      <c r="D89" s="5"/>
+      <c r="E89" s="5"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="7"/>
+      <c r="B90" s="5"/>
+      <c r="C90" s="5"/>
+      <c r="D90" s="5"/>
+      <c r="E90" s="5"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="7"/>
+      <c r="B91" s="5"/>
+      <c r="C91" s="5"/>
+      <c r="D91" s="5"/>
+      <c r="E91" s="5"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="7"/>
+      <c r="B92" s="5"/>
+      <c r="C92" s="5"/>
+      <c r="D92" s="5"/>
+      <c r="E92" s="5"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="7"/>
+      <c r="B93" s="5"/>
+      <c r="C93" s="5"/>
+      <c r="D93" s="5"/>
+      <c r="E93" s="5"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="7"/>
+      <c r="B94" s="5"/>
+      <c r="C94" s="5"/>
+      <c r="D94" s="5"/>
+      <c r="E94" s="5"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="7"/>
+      <c r="B95" s="5"/>
+      <c r="C95" s="5"/>
+      <c r="D95" s="5"/>
+      <c r="E95" s="5"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="7"/>
+      <c r="B96" s="5"/>
+      <c r="C96" s="5"/>
+      <c r="D96" s="5"/>
+      <c r="E96" s="5"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="7"/>
+      <c r="B97" s="5"/>
+      <c r="C97" s="5"/>
+      <c r="D97" s="5"/>
+      <c r="E97" s="5"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="7"/>
+      <c r="B98" s="5"/>
+      <c r="C98" s="5"/>
+      <c r="D98" s="5"/>
+      <c r="E98" s="5"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="7"/>
+      <c r="B99" s="5"/>
+      <c r="C99" s="5"/>
+      <c r="D99" s="5"/>
+      <c r="E99" s="5"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="7"/>
+      <c r="B100" s="5"/>
+      <c r="C100" s="5"/>
+      <c r="D100" s="5"/>
+      <c r="E100" s="5"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="7"/>
+      <c r="B101" s="5"/>
+      <c r="C101" s="5"/>
+      <c r="D101" s="5"/>
+      <c r="E101" s="5"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="7"/>
+      <c r="B102" s="5"/>
+      <c r="C102" s="5"/>
+      <c r="D102" s="5"/>
+      <c r="E102" s="5"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="7"/>
+      <c r="B103" s="5"/>
+      <c r="C103" s="5"/>
+      <c r="D103" s="5"/>
+      <c r="E103" s="5"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="7"/>
+      <c r="B104" s="5"/>
+      <c r="C104" s="5"/>
+      <c r="D104" s="5"/>
+      <c r="E104" s="5"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="7"/>
+      <c r="B105" s="5"/>
+      <c r="C105" s="5"/>
+      <c r="D105" s="5"/>
+      <c r="E105" s="5"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="7"/>
+      <c r="B106" s="5"/>
+      <c r="C106" s="5"/>
+      <c r="D106" s="5"/>
+      <c r="E106" s="5"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="7"/>
+      <c r="B107" s="5"/>
+      <c r="C107" s="5"/>
+      <c r="D107" s="5"/>
+      <c r="E107" s="5"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="7"/>
+      <c r="B108" s="5"/>
+      <c r="C108" s="5"/>
+      <c r="D108" s="5"/>
+      <c r="E108" s="5"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="7"/>
+      <c r="B109" s="5"/>
+      <c r="C109" s="5"/>
+      <c r="D109" s="5"/>
+      <c r="E109" s="5"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="7"/>
+      <c r="B110" s="5"/>
+      <c r="C110" s="5"/>
+      <c r="D110" s="5"/>
+      <c r="E110" s="5"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="7"/>
+      <c r="B111" s="5"/>
+      <c r="C111" s="5"/>
+      <c r="D111" s="5"/>
+      <c r="E111" s="5"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="7"/>
+      <c r="B112" s="5"/>
+      <c r="C112" s="5"/>
+      <c r="D112" s="5"/>
+      <c r="E112" s="5"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="7"/>
+      <c r="B113" s="5"/>
+      <c r="C113" s="5"/>
+      <c r="D113" s="5"/>
+      <c r="E113" s="5"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="7"/>
+      <c r="B114" s="5"/>
+      <c r="C114" s="5"/>
+      <c r="D114" s="5"/>
+      <c r="E114" s="5"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="7"/>
+      <c r="B115" s="5"/>
+      <c r="C115" s="5"/>
+      <c r="D115" s="5"/>
+      <c r="E115" s="5"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="7"/>
+      <c r="B116" s="5"/>
+      <c r="C116" s="5"/>
+      <c r="D116" s="5"/>
+      <c r="E116" s="5"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="7"/>
+      <c r="B117" s="5"/>
+      <c r="C117" s="5"/>
+      <c r="D117" s="5"/>
+      <c r="E117" s="5"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="7"/>
+      <c r="B118" s="5"/>
+      <c r="C118" s="5"/>
+      <c r="D118" s="5"/>
+      <c r="E118" s="5"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="7"/>
+      <c r="B119" s="5"/>
+      <c r="C119" s="5"/>
+      <c r="D119" s="5"/>
+      <c r="E119" s="5"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="7"/>
+      <c r="B120" s="5"/>
+      <c r="C120" s="5"/>
+      <c r="D120" s="5"/>
+      <c r="E120" s="5"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="7"/>
+      <c r="B121" s="5"/>
+      <c r="C121" s="5"/>
+      <c r="D121" s="5"/>
+      <c r="E121" s="5"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="7"/>
+      <c r="B122" s="5"/>
+      <c r="C122" s="5"/>
+      <c r="D122" s="5"/>
+      <c r="E122" s="5"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="7"/>
+      <c r="B123" s="5"/>
+      <c r="C123" s="5"/>
+      <c r="D123" s="5"/>
+      <c r="E123" s="5"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="7"/>
+      <c r="B124" s="5"/>
+      <c r="C124" s="5"/>
+      <c r="D124" s="5"/>
+      <c r="E124" s="5"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="7"/>
+      <c r="B125" s="5"/>
+      <c r="C125" s="5"/>
+      <c r="D125" s="5"/>
+      <c r="E125" s="5"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="7"/>
+      <c r="B126" s="5"/>
+      <c r="C126" s="5"/>
+      <c r="D126" s="5"/>
+      <c r="E126" s="5"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="7"/>
+      <c r="B127" s="5"/>
+      <c r="C127" s="5"/>
+      <c r="D127" s="5"/>
+      <c r="E127" s="5"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="7"/>
+      <c r="B128" s="5"/>
+      <c r="C128" s="5"/>
+      <c r="D128" s="5"/>
+      <c r="E128" s="5"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="7"/>
+      <c r="B129" s="5"/>
+      <c r="C129" s="5"/>
+      <c r="D129" s="5"/>
+      <c r="E129" s="5"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="7"/>
+      <c r="B130" s="5"/>
+      <c r="C130" s="5"/>
+      <c r="D130" s="5"/>
+      <c r="E130" s="5"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="7"/>
+      <c r="B131" s="5"/>
+      <c r="C131" s="5"/>
+      <c r="D131" s="5"/>
+      <c r="E131" s="5"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="7"/>
+      <c r="B132" s="5"/>
+      <c r="C132" s="5"/>
+      <c r="D132" s="5"/>
+      <c r="E132" s="5"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="7"/>
+      <c r="B133" s="5"/>
+      <c r="C133" s="5"/>
+      <c r="D133" s="5"/>
+      <c r="E133" s="5"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="7"/>
+      <c r="B134" s="5"/>
+      <c r="C134" s="5"/>
+      <c r="D134" s="5"/>
+      <c r="E134" s="5"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="7"/>
+      <c r="B135" s="5"/>
+      <c r="C135" s="5"/>
+      <c r="D135" s="5"/>
+      <c r="E135" s="5"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="7"/>
+      <c r="B136" s="5"/>
+      <c r="C136" s="5"/>
+      <c r="D136" s="5"/>
+      <c r="E136" s="5"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="7"/>
+      <c r="B137" s="5"/>
+      <c r="C137" s="5"/>
+      <c r="D137" s="5"/>
+      <c r="E137" s="5"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="7"/>
+      <c r="B138" s="5"/>
+      <c r="C138" s="5"/>
+      <c r="D138" s="5"/>
+      <c r="E138" s="5"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="7"/>
+      <c r="B139" s="5"/>
+      <c r="C139" s="5"/>
+      <c r="D139" s="5"/>
+      <c r="E139" s="5"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="7"/>
+      <c r="B140" s="5"/>
+      <c r="C140" s="5"/>
+      <c r="D140" s="5"/>
+      <c r="E140" s="5"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="7"/>
+      <c r="B141" s="5"/>
+      <c r="C141" s="5"/>
+      <c r="D141" s="5"/>
+      <c r="E141" s="5"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="7"/>
+      <c r="B142" s="5"/>
+      <c r="C142" s="5"/>
+      <c r="D142" s="5"/>
+      <c r="E142" s="5"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="7"/>
+      <c r="B143" s="5"/>
+      <c r="C143" s="5"/>
+      <c r="D143" s="5"/>
+      <c r="E143" s="5"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="7"/>
+      <c r="B144" s="5"/>
+      <c r="C144" s="5"/>
+      <c r="D144" s="5"/>
+      <c r="E144" s="5"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="7"/>
+      <c r="B145" s="5"/>
+      <c r="C145" s="5"/>
+      <c r="D145" s="5"/>
+      <c r="E145" s="5"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="7"/>
+      <c r="B146" s="5"/>
+      <c r="C146" s="5"/>
+      <c r="D146" s="5"/>
+      <c r="E146" s="5"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="7"/>
+      <c r="B147" s="5"/>
+      <c r="C147" s="5"/>
+      <c r="D147" s="5"/>
+      <c r="E147" s="5"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="7"/>
+      <c r="B148" s="5"/>
+      <c r="C148" s="5"/>
+      <c r="D148" s="5"/>
+      <c r="E148" s="5"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="7"/>
+      <c r="B149" s="5"/>
+      <c r="C149" s="5"/>
+      <c r="D149" s="5"/>
+      <c r="E149" s="5"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="7"/>
+      <c r="B150" s="5"/>
+      <c r="C150" s="5"/>
+      <c r="D150" s="5"/>
+      <c r="E150" s="5"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="7"/>
+      <c r="B151" s="5"/>
+      <c r="C151" s="5"/>
+      <c r="D151" s="5"/>
+      <c r="E151" s="5"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="7"/>
+      <c r="B152" s="5"/>
+      <c r="C152" s="5"/>
+      <c r="D152" s="5"/>
+      <c r="E152" s="5"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="7"/>
+      <c r="B153" s="5"/>
+      <c r="C153" s="5"/>
+      <c r="D153" s="5"/>
+      <c r="E153" s="5"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="7"/>
+      <c r="B154" s="5"/>
+      <c r="C154" s="5"/>
+      <c r="D154" s="5"/>
+      <c r="E154" s="5"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="7"/>
+      <c r="B155" s="5"/>
+      <c r="C155" s="5"/>
+      <c r="D155" s="5"/>
+      <c r="E155" s="5"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="7"/>
+      <c r="B156" s="5"/>
+      <c r="C156" s="5"/>
+      <c r="D156" s="5"/>
+      <c r="E156" s="5"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="7"/>
+      <c r="B157" s="5"/>
+      <c r="C157" s="5"/>
+      <c r="D157" s="5"/>
+      <c r="E157" s="5"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="7"/>
+      <c r="B158" s="5"/>
+      <c r="C158" s="5"/>
+      <c r="D158" s="5"/>
+      <c r="E158" s="5"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="7"/>
+      <c r="B159" s="5"/>
+      <c r="C159" s="5"/>
+      <c r="D159" s="5"/>
+      <c r="E159" s="5"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="7"/>
+      <c r="B160" s="5"/>
+      <c r="C160" s="5"/>
+      <c r="D160" s="5"/>
+      <c r="E160" s="5"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="7"/>
+      <c r="B161" s="5"/>
+      <c r="C161" s="5"/>
+      <c r="D161" s="5"/>
+      <c r="E161" s="5"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="7"/>
+      <c r="B162" s="5"/>
+      <c r="C162" s="5"/>
+      <c r="D162" s="5"/>
+      <c r="E162" s="5"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="7"/>
+      <c r="B163" s="5"/>
+      <c r="C163" s="5"/>
+      <c r="D163" s="5"/>
+      <c r="E163" s="5"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="7"/>
+      <c r="B164" s="5"/>
+      <c r="C164" s="5"/>
+      <c r="D164" s="5"/>
+      <c r="E164" s="5"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="7"/>
+      <c r="B165" s="5"/>
+      <c r="C165" s="5"/>
+      <c r="D165" s="5"/>
+      <c r="E165" s="5"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="7"/>
+      <c r="B166" s="5"/>
+      <c r="C166" s="5"/>
+      <c r="D166" s="5"/>
+      <c r="E166" s="5"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="7"/>
+      <c r="B167" s="5"/>
+      <c r="C167" s="5"/>
+      <c r="D167" s="5"/>
+      <c r="E167" s="5"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="7"/>
+      <c r="B168" s="5"/>
+      <c r="C168" s="5"/>
+      <c r="D168" s="5"/>
+      <c r="E168" s="5"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="7"/>
+      <c r="B169" s="5"/>
+      <c r="C169" s="5"/>
+      <c r="D169" s="5"/>
+      <c r="E169" s="5"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="7"/>
+      <c r="B170" s="5"/>
+      <c r="C170" s="5"/>
+      <c r="D170" s="5"/>
+      <c r="E170" s="5"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="7"/>
+      <c r="B171" s="5"/>
+      <c r="C171" s="5"/>
+      <c r="D171" s="5"/>
+      <c r="E171" s="5"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="7"/>
+      <c r="B172" s="5"/>
+      <c r="C172" s="5"/>
+      <c r="D172" s="5"/>
+      <c r="E172" s="5"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="7"/>
+      <c r="B173" s="5"/>
+      <c r="C173" s="5"/>
+      <c r="D173" s="5"/>
+      <c r="E173" s="5"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="7"/>
+      <c r="B174" s="5"/>
+      <c r="C174" s="5"/>
+      <c r="D174" s="5"/>
+      <c r="E174" s="5"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="7"/>
+      <c r="B175" s="5"/>
+      <c r="C175" s="5"/>
+      <c r="D175" s="5"/>
+      <c r="E175" s="5"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="7"/>
+      <c r="B176" s="5"/>
+      <c r="C176" s="5"/>
+      <c r="D176" s="5"/>
+      <c r="E176" s="5"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="7"/>
+      <c r="B177" s="5"/>
+      <c r="C177" s="5"/>
+      <c r="D177" s="5"/>
+      <c r="E177" s="5"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="7"/>
+      <c r="B178" s="5"/>
+      <c r="C178" s="5"/>
+      <c r="D178" s="5"/>
+      <c r="E178" s="5"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="7"/>
+      <c r="B179" s="5"/>
+      <c r="C179" s="5"/>
+      <c r="D179" s="5"/>
+      <c r="E179" s="5"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="7"/>
+      <c r="B180" s="5"/>
+      <c r="C180" s="5"/>
+      <c r="D180" s="5"/>
+      <c r="E180" s="5"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="7"/>
+      <c r="B181" s="5"/>
+      <c r="C181" s="5"/>
+      <c r="D181" s="5"/>
+      <c r="E181" s="5"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="7"/>
+      <c r="B182" s="5"/>
+      <c r="C182" s="5"/>
+      <c r="D182" s="5"/>
+      <c r="E182" s="5"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="7"/>
+      <c r="B183" s="5"/>
+      <c r="C183" s="5"/>
+      <c r="D183" s="5"/>
+      <c r="E183" s="5"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="7"/>
+      <c r="B184" s="5"/>
+      <c r="C184" s="5"/>
+      <c r="D184" s="5"/>
+      <c r="E184" s="5"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="7"/>
+      <c r="B185" s="5"/>
+      <c r="C185" s="5"/>
+      <c r="D185" s="5"/>
+      <c r="E185" s="5"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="7"/>
+      <c r="B186" s="5"/>
+      <c r="C186" s="5"/>
+      <c r="D186" s="5"/>
+      <c r="E186" s="5"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="7"/>
+      <c r="B187" s="5"/>
+      <c r="C187" s="5"/>
+      <c r="D187" s="5"/>
+      <c r="E187" s="5"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="7"/>
+      <c r="B188" s="5"/>
+      <c r="C188" s="5"/>
+      <c r="D188" s="5"/>
+      <c r="E188" s="5"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="7"/>
+      <c r="B189" s="5"/>
+      <c r="C189" s="5"/>
+      <c r="D189" s="5"/>
+      <c r="E189" s="5"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="7"/>
+      <c r="B190" s="5"/>
+      <c r="C190" s="5"/>
+      <c r="D190" s="5"/>
+      <c r="E190" s="5"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="7"/>
+      <c r="B191" s="5"/>
+      <c r="C191" s="5"/>
+      <c r="D191" s="5"/>
+      <c r="E191" s="5"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="7"/>
+      <c r="B192" s="5"/>
+      <c r="C192" s="5"/>
+      <c r="D192" s="5"/>
+      <c r="E192" s="5"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="7"/>
+      <c r="B193" s="5"/>
+      <c r="C193" s="5"/>
+      <c r="D193" s="5"/>
+      <c r="E193" s="5"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="7"/>
+      <c r="B194" s="5"/>
+      <c r="C194" s="5"/>
+      <c r="D194" s="5"/>
+      <c r="E194" s="5"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="7"/>
+      <c r="B195" s="5"/>
+      <c r="C195" s="5"/>
+      <c r="D195" s="5"/>
+      <c r="E195" s="5"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="7"/>
+      <c r="B196" s="5"/>
+      <c r="C196" s="5"/>
+      <c r="D196" s="5"/>
+      <c r="E196" s="5"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="7"/>
+      <c r="B197" s="5"/>
+      <c r="C197" s="5"/>
+      <c r="D197" s="5"/>
+      <c r="E197" s="5"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="7"/>
+      <c r="B198" s="5"/>
+      <c r="C198" s="5"/>
+      <c r="D198" s="5"/>
+      <c r="E198" s="5"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="7"/>
+      <c r="B199" s="5"/>
+      <c r="C199" s="5"/>
+      <c r="D199" s="5"/>
+      <c r="E199" s="5"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="7"/>
+      <c r="B200" s="5"/>
+      <c r="C200" s="5"/>
+      <c r="D200" s="5"/>
+      <c r="E200" s="5"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="7"/>
+      <c r="B201" s="5"/>
+      <c r="C201" s="5"/>
+      <c r="D201" s="5"/>
+      <c r="E201" s="5"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="7"/>
+      <c r="B202" s="5"/>
+      <c r="C202" s="5"/>
+      <c r="D202" s="5"/>
+      <c r="E202" s="5"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="7"/>
+      <c r="B203" s="5"/>
+      <c r="C203" s="5"/>
+      <c r="D203" s="5"/>
+      <c r="E203" s="5"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="7"/>
+      <c r="B204" s="5"/>
+      <c r="C204" s="5"/>
+      <c r="D204" s="5"/>
+      <c r="E204" s="5"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="7"/>
+      <c r="B205" s="5"/>
+      <c r="C205" s="5"/>
+      <c r="D205" s="5"/>
+      <c r="E205" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A5:E5"/>
+  </mergeCells>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF0D5C45"/>
@@ -370,7 +3614,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Type the name, then the date each course was done under "Done on". The tinted Expires cell beside it fills in by itself.</t>
+          <t>Type the name, then the date each course was done under "Done on". The tinted Expires cell beside it fills in by itself. The eight courses and renewal periods here are common ones, not a rule: your statement of purpose and risk assessments set your list, so rename the headings and change the months in the formulas to match.</t>
         </is>
       </c>
     </row>
@@ -432,82 +3676,82 @@
     </row>
     <row r="5">
       <c r="A5" s="4"/>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>Done on</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>Expires (auto)</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="12" t="inlineStr">
         <is>
           <t>Done on</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="12" t="inlineStr">
         <is>
           <t>Expires (auto)</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F5" s="12" t="inlineStr">
         <is>
           <t>Done on</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" s="12" t="inlineStr">
         <is>
           <t>Expires (auto)</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
+      <c r="H5" s="12" t="inlineStr">
         <is>
           <t>Done on</t>
         </is>
       </c>
-      <c r="I5" s="7" t="inlineStr">
+      <c r="I5" s="12" t="inlineStr">
         <is>
           <t>Expires (auto)</t>
         </is>
       </c>
-      <c r="J5" s="7" t="inlineStr">
+      <c r="J5" s="12" t="inlineStr">
         <is>
           <t>Done on</t>
         </is>
       </c>
-      <c r="K5" s="7" t="inlineStr">
+      <c r="K5" s="12" t="inlineStr">
         <is>
           <t>Expires (auto)</t>
         </is>
       </c>
-      <c r="L5" s="7" t="inlineStr">
+      <c r="L5" s="12" t="inlineStr">
         <is>
           <t>Done on</t>
         </is>
       </c>
-      <c r="M5" s="7" t="inlineStr">
+      <c r="M5" s="12" t="inlineStr">
         <is>
           <t>Expires (auto)</t>
         </is>
       </c>
-      <c r="N5" s="7" t="inlineStr">
+      <c r="N5" s="12" t="inlineStr">
         <is>
           <t>Done on</t>
         </is>
       </c>
-      <c r="O5" s="7" t="inlineStr">
+      <c r="O5" s="12" t="inlineStr">
         <is>
           <t>Expires (auto)</t>
         </is>
       </c>
-      <c r="P5" s="7" t="inlineStr">
+      <c r="P5" s="12" t="inlineStr">
         <is>
           <t>Done on</t>
         </is>
       </c>
-      <c r="Q5" s="7" t="inlineStr">
+      <c r="Q5" s="12" t="inlineStr">
         <is>
           <t>Expires (auto)</t>
         </is>
@@ -519,741 +3763,741 @@
           <t>Example, overtype or delete me</t>
         </is>
       </c>
-      <c r="B6" s="9">
-        <v>45862</v>
+      <c r="B6" s="11">
+        <v>45871</v>
       </c>
       <c r="C6" s="10">
         <f>IF(B6="","",EDATE(B6,12))</f>
       </c>
-      <c r="D6" s="9">
-        <v>45261</v>
+      <c r="D6" s="11">
+        <v>45271</v>
       </c>
       <c r="E6" s="10">
         <f>IF(D6="","",EDATE(D6,36))</f>
       </c>
-      <c r="F6" s="9">
-        <v>45912</v>
+      <c r="F6" s="11">
+        <v>45921</v>
       </c>
       <c r="G6" s="10">
         <f>IF(F6="","",EDATE(F6,12))</f>
       </c>
-      <c r="H6" s="11"/>
+      <c r="H6" s="7"/>
       <c r="I6" s="10">
         <f>IF(H6="","",EDATE(H6,12))</f>
       </c>
-      <c r="J6" s="11"/>
+      <c r="J6" s="7"/>
       <c r="K6" s="10">
         <f>IF(J6="","",EDATE(J6,36))</f>
       </c>
-      <c r="L6" s="11"/>
+      <c r="L6" s="7"/>
       <c r="M6" s="10">
         <f>IF(L6="","",EDATE(L6,12))</f>
       </c>
-      <c r="N6" s="11"/>
+      <c r="N6" s="7"/>
       <c r="O6" s="10">
         <f>IF(N6="","",EDATE(N6,12))</f>
       </c>
-      <c r="P6" s="11"/>
+      <c r="P6" s="7"/>
       <c r="Q6" s="10">
         <f>IF(P6="","",EDATE(P6,24))</f>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5"/>
-      <c r="B7" s="11"/>
+      <c r="B7" s="7"/>
       <c r="C7" s="10">
         <f>IF(B7="","",EDATE(B7,12))</f>
       </c>
-      <c r="D7" s="11"/>
+      <c r="D7" s="7"/>
       <c r="E7" s="10">
         <f>IF(D7="","",EDATE(D7,36))</f>
       </c>
-      <c r="F7" s="11"/>
+      <c r="F7" s="7"/>
       <c r="G7" s="10">
         <f>IF(F7="","",EDATE(F7,12))</f>
       </c>
-      <c r="H7" s="11"/>
+      <c r="H7" s="7"/>
       <c r="I7" s="10">
         <f>IF(H7="","",EDATE(H7,12))</f>
       </c>
-      <c r="J7" s="11"/>
+      <c r="J7" s="7"/>
       <c r="K7" s="10">
         <f>IF(J7="","",EDATE(J7,36))</f>
       </c>
-      <c r="L7" s="11"/>
+      <c r="L7" s="7"/>
       <c r="M7" s="10">
         <f>IF(L7="","",EDATE(L7,12))</f>
       </c>
-      <c r="N7" s="11"/>
+      <c r="N7" s="7"/>
       <c r="O7" s="10">
         <f>IF(N7="","",EDATE(N7,12))</f>
       </c>
-      <c r="P7" s="11"/>
+      <c r="P7" s="7"/>
       <c r="Q7" s="10">
         <f>IF(P7="","",EDATE(P7,24))</f>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5"/>
-      <c r="B8" s="11"/>
+      <c r="B8" s="7"/>
       <c r="C8" s="10">
         <f>IF(B8="","",EDATE(B8,12))</f>
       </c>
-      <c r="D8" s="11"/>
+      <c r="D8" s="7"/>
       <c r="E8" s="10">
         <f>IF(D8="","",EDATE(D8,36))</f>
       </c>
-      <c r="F8" s="11"/>
+      <c r="F8" s="7"/>
       <c r="G8" s="10">
         <f>IF(F8="","",EDATE(F8,12))</f>
       </c>
-      <c r="H8" s="11"/>
+      <c r="H8" s="7"/>
       <c r="I8" s="10">
         <f>IF(H8="","",EDATE(H8,12))</f>
       </c>
-      <c r="J8" s="11"/>
+      <c r="J8" s="7"/>
       <c r="K8" s="10">
         <f>IF(J8="","",EDATE(J8,36))</f>
       </c>
-      <c r="L8" s="11"/>
+      <c r="L8" s="7"/>
       <c r="M8" s="10">
         <f>IF(L8="","",EDATE(L8,12))</f>
       </c>
-      <c r="N8" s="11"/>
+      <c r="N8" s="7"/>
       <c r="O8" s="10">
         <f>IF(N8="","",EDATE(N8,12))</f>
       </c>
-      <c r="P8" s="11"/>
+      <c r="P8" s="7"/>
       <c r="Q8" s="10">
         <f>IF(P8="","",EDATE(P8,24))</f>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5"/>
-      <c r="B9" s="11"/>
+      <c r="B9" s="7"/>
       <c r="C9" s="10">
         <f>IF(B9="","",EDATE(B9,12))</f>
       </c>
-      <c r="D9" s="11"/>
+      <c r="D9" s="7"/>
       <c r="E9" s="10">
         <f>IF(D9="","",EDATE(D9,36))</f>
       </c>
-      <c r="F9" s="11"/>
+      <c r="F9" s="7"/>
       <c r="G9" s="10">
         <f>IF(F9="","",EDATE(F9,12))</f>
       </c>
-      <c r="H9" s="11"/>
+      <c r="H9" s="7"/>
       <c r="I9" s="10">
         <f>IF(H9="","",EDATE(H9,12))</f>
       </c>
-      <c r="J9" s="11"/>
+      <c r="J9" s="7"/>
       <c r="K9" s="10">
         <f>IF(J9="","",EDATE(J9,36))</f>
       </c>
-      <c r="L9" s="11"/>
+      <c r="L9" s="7"/>
       <c r="M9" s="10">
         <f>IF(L9="","",EDATE(L9,12))</f>
       </c>
-      <c r="N9" s="11"/>
+      <c r="N9" s="7"/>
       <c r="O9" s="10">
         <f>IF(N9="","",EDATE(N9,12))</f>
       </c>
-      <c r="P9" s="11"/>
+      <c r="P9" s="7"/>
       <c r="Q9" s="10">
         <f>IF(P9="","",EDATE(P9,24))</f>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5"/>
-      <c r="B10" s="11"/>
+      <c r="B10" s="7"/>
       <c r="C10" s="10">
         <f>IF(B10="","",EDATE(B10,12))</f>
       </c>
-      <c r="D10" s="11"/>
+      <c r="D10" s="7"/>
       <c r="E10" s="10">
         <f>IF(D10="","",EDATE(D10,36))</f>
       </c>
-      <c r="F10" s="11"/>
+      <c r="F10" s="7"/>
       <c r="G10" s="10">
         <f>IF(F10="","",EDATE(F10,12))</f>
       </c>
-      <c r="H10" s="11"/>
+      <c r="H10" s="7"/>
       <c r="I10" s="10">
         <f>IF(H10="","",EDATE(H10,12))</f>
       </c>
-      <c r="J10" s="11"/>
+      <c r="J10" s="7"/>
       <c r="K10" s="10">
         <f>IF(J10="","",EDATE(J10,36))</f>
       </c>
-      <c r="L10" s="11"/>
+      <c r="L10" s="7"/>
       <c r="M10" s="10">
         <f>IF(L10="","",EDATE(L10,12))</f>
       </c>
-      <c r="N10" s="11"/>
+      <c r="N10" s="7"/>
       <c r="O10" s="10">
         <f>IF(N10="","",EDATE(N10,12))</f>
       </c>
-      <c r="P10" s="11"/>
+      <c r="P10" s="7"/>
       <c r="Q10" s="10">
         <f>IF(P10="","",EDATE(P10,24))</f>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5"/>
-      <c r="B11" s="11"/>
+      <c r="B11" s="7"/>
       <c r="C11" s="10">
         <f>IF(B11="","",EDATE(B11,12))</f>
       </c>
-      <c r="D11" s="11"/>
+      <c r="D11" s="7"/>
       <c r="E11" s="10">
         <f>IF(D11="","",EDATE(D11,36))</f>
       </c>
-      <c r="F11" s="11"/>
+      <c r="F11" s="7"/>
       <c r="G11" s="10">
         <f>IF(F11="","",EDATE(F11,12))</f>
       </c>
-      <c r="H11" s="11"/>
+      <c r="H11" s="7"/>
       <c r="I11" s="10">
         <f>IF(H11="","",EDATE(H11,12))</f>
       </c>
-      <c r="J11" s="11"/>
+      <c r="J11" s="7"/>
       <c r="K11" s="10">
         <f>IF(J11="","",EDATE(J11,36))</f>
       </c>
-      <c r="L11" s="11"/>
+      <c r="L11" s="7"/>
       <c r="M11" s="10">
         <f>IF(L11="","",EDATE(L11,12))</f>
       </c>
-      <c r="N11" s="11"/>
+      <c r="N11" s="7"/>
       <c r="O11" s="10">
         <f>IF(N11="","",EDATE(N11,12))</f>
       </c>
-      <c r="P11" s="11"/>
+      <c r="P11" s="7"/>
       <c r="Q11" s="10">
         <f>IF(P11="","",EDATE(P11,24))</f>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5"/>
-      <c r="B12" s="11"/>
+      <c r="B12" s="7"/>
       <c r="C12" s="10">
         <f>IF(B12="","",EDATE(B12,12))</f>
       </c>
-      <c r="D12" s="11"/>
+      <c r="D12" s="7"/>
       <c r="E12" s="10">
         <f>IF(D12="","",EDATE(D12,36))</f>
       </c>
-      <c r="F12" s="11"/>
+      <c r="F12" s="7"/>
       <c r="G12" s="10">
         <f>IF(F12="","",EDATE(F12,12))</f>
       </c>
-      <c r="H12" s="11"/>
+      <c r="H12" s="7"/>
       <c r="I12" s="10">
         <f>IF(H12="","",EDATE(H12,12))</f>
       </c>
-      <c r="J12" s="11"/>
+      <c r="J12" s="7"/>
       <c r="K12" s="10">
         <f>IF(J12="","",EDATE(J12,36))</f>
       </c>
-      <c r="L12" s="11"/>
+      <c r="L12" s="7"/>
       <c r="M12" s="10">
         <f>IF(L12="","",EDATE(L12,12))</f>
       </c>
-      <c r="N12" s="11"/>
+      <c r="N12" s="7"/>
       <c r="O12" s="10">
         <f>IF(N12="","",EDATE(N12,12))</f>
       </c>
-      <c r="P12" s="11"/>
+      <c r="P12" s="7"/>
       <c r="Q12" s="10">
         <f>IF(P12="","",EDATE(P12,24))</f>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5"/>
-      <c r="B13" s="11"/>
+      <c r="B13" s="7"/>
       <c r="C13" s="10">
         <f>IF(B13="","",EDATE(B13,12))</f>
       </c>
-      <c r="D13" s="11"/>
+      <c r="D13" s="7"/>
       <c r="E13" s="10">
         <f>IF(D13="","",EDATE(D13,36))</f>
       </c>
-      <c r="F13" s="11"/>
+      <c r="F13" s="7"/>
       <c r="G13" s="10">
         <f>IF(F13="","",EDATE(F13,12))</f>
       </c>
-      <c r="H13" s="11"/>
+      <c r="H13" s="7"/>
       <c r="I13" s="10">
         <f>IF(H13="","",EDATE(H13,12))</f>
       </c>
-      <c r="J13" s="11"/>
+      <c r="J13" s="7"/>
       <c r="K13" s="10">
         <f>IF(J13="","",EDATE(J13,36))</f>
       </c>
-      <c r="L13" s="11"/>
+      <c r="L13" s="7"/>
       <c r="M13" s="10">
         <f>IF(L13="","",EDATE(L13,12))</f>
       </c>
-      <c r="N13" s="11"/>
+      <c r="N13" s="7"/>
       <c r="O13" s="10">
         <f>IF(N13="","",EDATE(N13,12))</f>
       </c>
-      <c r="P13" s="11"/>
+      <c r="P13" s="7"/>
       <c r="Q13" s="10">
         <f>IF(P13="","",EDATE(P13,24))</f>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5"/>
-      <c r="B14" s="11"/>
+      <c r="B14" s="7"/>
       <c r="C14" s="10">
         <f>IF(B14="","",EDATE(B14,12))</f>
       </c>
-      <c r="D14" s="11"/>
+      <c r="D14" s="7"/>
       <c r="E14" s="10">
         <f>IF(D14="","",EDATE(D14,36))</f>
       </c>
-      <c r="F14" s="11"/>
+      <c r="F14" s="7"/>
       <c r="G14" s="10">
         <f>IF(F14="","",EDATE(F14,12))</f>
       </c>
-      <c r="H14" s="11"/>
+      <c r="H14" s="7"/>
       <c r="I14" s="10">
         <f>IF(H14="","",EDATE(H14,12))</f>
       </c>
-      <c r="J14" s="11"/>
+      <c r="J14" s="7"/>
       <c r="K14" s="10">
         <f>IF(J14="","",EDATE(J14,36))</f>
       </c>
-      <c r="L14" s="11"/>
+      <c r="L14" s="7"/>
       <c r="M14" s="10">
         <f>IF(L14="","",EDATE(L14,12))</f>
       </c>
-      <c r="N14" s="11"/>
+      <c r="N14" s="7"/>
       <c r="O14" s="10">
         <f>IF(N14="","",EDATE(N14,12))</f>
       </c>
-      <c r="P14" s="11"/>
+      <c r="P14" s="7"/>
       <c r="Q14" s="10">
         <f>IF(P14="","",EDATE(P14,24))</f>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5"/>
-      <c r="B15" s="11"/>
+      <c r="B15" s="7"/>
       <c r="C15" s="10">
         <f>IF(B15="","",EDATE(B15,12))</f>
       </c>
-      <c r="D15" s="11"/>
+      <c r="D15" s="7"/>
       <c r="E15" s="10">
         <f>IF(D15="","",EDATE(D15,36))</f>
       </c>
-      <c r="F15" s="11"/>
+      <c r="F15" s="7"/>
       <c r="G15" s="10">
         <f>IF(F15="","",EDATE(F15,12))</f>
       </c>
-      <c r="H15" s="11"/>
+      <c r="H15" s="7"/>
       <c r="I15" s="10">
         <f>IF(H15="","",EDATE(H15,12))</f>
       </c>
-      <c r="J15" s="11"/>
+      <c r="J15" s="7"/>
       <c r="K15" s="10">
         <f>IF(J15="","",EDATE(J15,36))</f>
       </c>
-      <c r="L15" s="11"/>
+      <c r="L15" s="7"/>
       <c r="M15" s="10">
         <f>IF(L15="","",EDATE(L15,12))</f>
       </c>
-      <c r="N15" s="11"/>
+      <c r="N15" s="7"/>
       <c r="O15" s="10">
         <f>IF(N15="","",EDATE(N15,12))</f>
       </c>
-      <c r="P15" s="11"/>
+      <c r="P15" s="7"/>
       <c r="Q15" s="10">
         <f>IF(P15="","",EDATE(P15,24))</f>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5"/>
-      <c r="B16" s="11"/>
+      <c r="B16" s="7"/>
       <c r="C16" s="10">
         <f>IF(B16="","",EDATE(B16,12))</f>
       </c>
-      <c r="D16" s="11"/>
+      <c r="D16" s="7"/>
       <c r="E16" s="10">
         <f>IF(D16="","",EDATE(D16,36))</f>
       </c>
-      <c r="F16" s="11"/>
+      <c r="F16" s="7"/>
       <c r="G16" s="10">
         <f>IF(F16="","",EDATE(F16,12))</f>
       </c>
-      <c r="H16" s="11"/>
+      <c r="H16" s="7"/>
       <c r="I16" s="10">
         <f>IF(H16="","",EDATE(H16,12))</f>
       </c>
-      <c r="J16" s="11"/>
+      <c r="J16" s="7"/>
       <c r="K16" s="10">
         <f>IF(J16="","",EDATE(J16,36))</f>
       </c>
-      <c r="L16" s="11"/>
+      <c r="L16" s="7"/>
       <c r="M16" s="10">
         <f>IF(L16="","",EDATE(L16,12))</f>
       </c>
-      <c r="N16" s="11"/>
+      <c r="N16" s="7"/>
       <c r="O16" s="10">
         <f>IF(N16="","",EDATE(N16,12))</f>
       </c>
-      <c r="P16" s="11"/>
+      <c r="P16" s="7"/>
       <c r="Q16" s="10">
         <f>IF(P16="","",EDATE(P16,24))</f>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5"/>
-      <c r="B17" s="11"/>
+      <c r="B17" s="7"/>
       <c r="C17" s="10">
         <f>IF(B17="","",EDATE(B17,12))</f>
       </c>
-      <c r="D17" s="11"/>
+      <c r="D17" s="7"/>
       <c r="E17" s="10">
         <f>IF(D17="","",EDATE(D17,36))</f>
       </c>
-      <c r="F17" s="11"/>
+      <c r="F17" s="7"/>
       <c r="G17" s="10">
         <f>IF(F17="","",EDATE(F17,12))</f>
       </c>
-      <c r="H17" s="11"/>
+      <c r="H17" s="7"/>
       <c r="I17" s="10">
         <f>IF(H17="","",EDATE(H17,12))</f>
       </c>
-      <c r="J17" s="11"/>
+      <c r="J17" s="7"/>
       <c r="K17" s="10">
         <f>IF(J17="","",EDATE(J17,36))</f>
       </c>
-      <c r="L17" s="11"/>
+      <c r="L17" s="7"/>
       <c r="M17" s="10">
         <f>IF(L17="","",EDATE(L17,12))</f>
       </c>
-      <c r="N17" s="11"/>
+      <c r="N17" s="7"/>
       <c r="O17" s="10">
         <f>IF(N17="","",EDATE(N17,12))</f>
       </c>
-      <c r="P17" s="11"/>
+      <c r="P17" s="7"/>
       <c r="Q17" s="10">
         <f>IF(P17="","",EDATE(P17,24))</f>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5"/>
-      <c r="B18" s="11"/>
+      <c r="B18" s="7"/>
       <c r="C18" s="10">
         <f>IF(B18="","",EDATE(B18,12))</f>
       </c>
-      <c r="D18" s="11"/>
+      <c r="D18" s="7"/>
       <c r="E18" s="10">
         <f>IF(D18="","",EDATE(D18,36))</f>
       </c>
-      <c r="F18" s="11"/>
+      <c r="F18" s="7"/>
       <c r="G18" s="10">
         <f>IF(F18="","",EDATE(F18,12))</f>
       </c>
-      <c r="H18" s="11"/>
+      <c r="H18" s="7"/>
       <c r="I18" s="10">
         <f>IF(H18="","",EDATE(H18,12))</f>
       </c>
-      <c r="J18" s="11"/>
+      <c r="J18" s="7"/>
       <c r="K18" s="10">
         <f>IF(J18="","",EDATE(J18,36))</f>
       </c>
-      <c r="L18" s="11"/>
+      <c r="L18" s="7"/>
       <c r="M18" s="10">
         <f>IF(L18="","",EDATE(L18,12))</f>
       </c>
-      <c r="N18" s="11"/>
+      <c r="N18" s="7"/>
       <c r="O18" s="10">
         <f>IF(N18="","",EDATE(N18,12))</f>
       </c>
-      <c r="P18" s="11"/>
+      <c r="P18" s="7"/>
       <c r="Q18" s="10">
         <f>IF(P18="","",EDATE(P18,24))</f>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5"/>
-      <c r="B19" s="11"/>
+      <c r="B19" s="7"/>
       <c r="C19" s="10">
         <f>IF(B19="","",EDATE(B19,12))</f>
       </c>
-      <c r="D19" s="11"/>
+      <c r="D19" s="7"/>
       <c r="E19" s="10">
         <f>IF(D19="","",EDATE(D19,36))</f>
       </c>
-      <c r="F19" s="11"/>
+      <c r="F19" s="7"/>
       <c r="G19" s="10">
         <f>IF(F19="","",EDATE(F19,12))</f>
       </c>
-      <c r="H19" s="11"/>
+      <c r="H19" s="7"/>
       <c r="I19" s="10">
         <f>IF(H19="","",EDATE(H19,12))</f>
       </c>
-      <c r="J19" s="11"/>
+      <c r="J19" s="7"/>
       <c r="K19" s="10">
         <f>IF(J19="","",EDATE(J19,36))</f>
       </c>
-      <c r="L19" s="11"/>
+      <c r="L19" s="7"/>
       <c r="M19" s="10">
         <f>IF(L19="","",EDATE(L19,12))</f>
       </c>
-      <c r="N19" s="11"/>
+      <c r="N19" s="7"/>
       <c r="O19" s="10">
         <f>IF(N19="","",EDATE(N19,12))</f>
       </c>
-      <c r="P19" s="11"/>
+      <c r="P19" s="7"/>
       <c r="Q19" s="10">
         <f>IF(P19="","",EDATE(P19,24))</f>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5"/>
-      <c r="B20" s="11"/>
+      <c r="B20" s="7"/>
       <c r="C20" s="10">
         <f>IF(B20="","",EDATE(B20,12))</f>
       </c>
-      <c r="D20" s="11"/>
+      <c r="D20" s="7"/>
       <c r="E20" s="10">
         <f>IF(D20="","",EDATE(D20,36))</f>
       </c>
-      <c r="F20" s="11"/>
+      <c r="F20" s="7"/>
       <c r="G20" s="10">
         <f>IF(F20="","",EDATE(F20,12))</f>
       </c>
-      <c r="H20" s="11"/>
+      <c r="H20" s="7"/>
       <c r="I20" s="10">
         <f>IF(H20="","",EDATE(H20,12))</f>
       </c>
-      <c r="J20" s="11"/>
+      <c r="J20" s="7"/>
       <c r="K20" s="10">
         <f>IF(J20="","",EDATE(J20,36))</f>
       </c>
-      <c r="L20" s="11"/>
+      <c r="L20" s="7"/>
       <c r="M20" s="10">
         <f>IF(L20="","",EDATE(L20,12))</f>
       </c>
-      <c r="N20" s="11"/>
+      <c r="N20" s="7"/>
       <c r="O20" s="10">
         <f>IF(N20="","",EDATE(N20,12))</f>
       </c>
-      <c r="P20" s="11"/>
+      <c r="P20" s="7"/>
       <c r="Q20" s="10">
         <f>IF(P20="","",EDATE(P20,24))</f>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5"/>
-      <c r="B21" s="11"/>
+      <c r="B21" s="7"/>
       <c r="C21" s="10">
         <f>IF(B21="","",EDATE(B21,12))</f>
       </c>
-      <c r="D21" s="11"/>
+      <c r="D21" s="7"/>
       <c r="E21" s="10">
         <f>IF(D21="","",EDATE(D21,36))</f>
       </c>
-      <c r="F21" s="11"/>
+      <c r="F21" s="7"/>
       <c r="G21" s="10">
         <f>IF(F21="","",EDATE(F21,12))</f>
       </c>
-      <c r="H21" s="11"/>
+      <c r="H21" s="7"/>
       <c r="I21" s="10">
         <f>IF(H21="","",EDATE(H21,12))</f>
       </c>
-      <c r="J21" s="11"/>
+      <c r="J21" s="7"/>
       <c r="K21" s="10">
         <f>IF(J21="","",EDATE(J21,36))</f>
       </c>
-      <c r="L21" s="11"/>
+      <c r="L21" s="7"/>
       <c r="M21" s="10">
         <f>IF(L21="","",EDATE(L21,12))</f>
       </c>
-      <c r="N21" s="11"/>
+      <c r="N21" s="7"/>
       <c r="O21" s="10">
         <f>IF(N21="","",EDATE(N21,12))</f>
       </c>
-      <c r="P21" s="11"/>
+      <c r="P21" s="7"/>
       <c r="Q21" s="10">
         <f>IF(P21="","",EDATE(P21,24))</f>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5"/>
-      <c r="B22" s="11"/>
+      <c r="B22" s="7"/>
       <c r="C22" s="10">
         <f>IF(B22="","",EDATE(B22,12))</f>
       </c>
-      <c r="D22" s="11"/>
+      <c r="D22" s="7"/>
       <c r="E22" s="10">
         <f>IF(D22="","",EDATE(D22,36))</f>
       </c>
-      <c r="F22" s="11"/>
+      <c r="F22" s="7"/>
       <c r="G22" s="10">
         <f>IF(F22="","",EDATE(F22,12))</f>
       </c>
-      <c r="H22" s="11"/>
+      <c r="H22" s="7"/>
       <c r="I22" s="10">
         <f>IF(H22="","",EDATE(H22,12))</f>
       </c>
-      <c r="J22" s="11"/>
+      <c r="J22" s="7"/>
       <c r="K22" s="10">
         <f>IF(J22="","",EDATE(J22,36))</f>
       </c>
-      <c r="L22" s="11"/>
+      <c r="L22" s="7"/>
       <c r="M22" s="10">
         <f>IF(L22="","",EDATE(L22,12))</f>
       </c>
-      <c r="N22" s="11"/>
+      <c r="N22" s="7"/>
       <c r="O22" s="10">
         <f>IF(N22="","",EDATE(N22,12))</f>
       </c>
-      <c r="P22" s="11"/>
+      <c r="P22" s="7"/>
       <c r="Q22" s="10">
         <f>IF(P22="","",EDATE(P22,24))</f>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5"/>
-      <c r="B23" s="11"/>
+      <c r="B23" s="7"/>
       <c r="C23" s="10">
         <f>IF(B23="","",EDATE(B23,12))</f>
       </c>
-      <c r="D23" s="11"/>
+      <c r="D23" s="7"/>
       <c r="E23" s="10">
         <f>IF(D23="","",EDATE(D23,36))</f>
       </c>
-      <c r="F23" s="11"/>
+      <c r="F23" s="7"/>
       <c r="G23" s="10">
         <f>IF(F23="","",EDATE(F23,12))</f>
       </c>
-      <c r="H23" s="11"/>
+      <c r="H23" s="7"/>
       <c r="I23" s="10">
         <f>IF(H23="","",EDATE(H23,12))</f>
       </c>
-      <c r="J23" s="11"/>
+      <c r="J23" s="7"/>
       <c r="K23" s="10">
         <f>IF(J23="","",EDATE(J23,36))</f>
       </c>
-      <c r="L23" s="11"/>
+      <c r="L23" s="7"/>
       <c r="M23" s="10">
         <f>IF(L23="","",EDATE(L23,12))</f>
       </c>
-      <c r="N23" s="11"/>
+      <c r="N23" s="7"/>
       <c r="O23" s="10">
         <f>IF(N23="","",EDATE(N23,12))</f>
       </c>
-      <c r="P23" s="11"/>
+      <c r="P23" s="7"/>
       <c r="Q23" s="10">
         <f>IF(P23="","",EDATE(P23,24))</f>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5"/>
-      <c r="B24" s="11"/>
+      <c r="B24" s="7"/>
       <c r="C24" s="10">
         <f>IF(B24="","",EDATE(B24,12))</f>
       </c>
-      <c r="D24" s="11"/>
+      <c r="D24" s="7"/>
       <c r="E24" s="10">
         <f>IF(D24="","",EDATE(D24,36))</f>
       </c>
-      <c r="F24" s="11"/>
+      <c r="F24" s="7"/>
       <c r="G24" s="10">
         <f>IF(F24="","",EDATE(F24,12))</f>
       </c>
-      <c r="H24" s="11"/>
+      <c r="H24" s="7"/>
       <c r="I24" s="10">
         <f>IF(H24="","",EDATE(H24,12))</f>
       </c>
-      <c r="J24" s="11"/>
+      <c r="J24" s="7"/>
       <c r="K24" s="10">
         <f>IF(J24="","",EDATE(J24,36))</f>
       </c>
-      <c r="L24" s="11"/>
+      <c r="L24" s="7"/>
       <c r="M24" s="10">
         <f>IF(L24="","",EDATE(L24,12))</f>
       </c>
-      <c r="N24" s="11"/>
+      <c r="N24" s="7"/>
       <c r="O24" s="10">
         <f>IF(N24="","",EDATE(N24,12))</f>
       </c>
-      <c r="P24" s="11"/>
+      <c r="P24" s="7"/>
       <c r="Q24" s="10">
         <f>IF(P24="","",EDATE(P24,24))</f>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5"/>
-      <c r="B25" s="11"/>
+      <c r="B25" s="7"/>
       <c r="C25" s="10">
         <f>IF(B25="","",EDATE(B25,12))</f>
       </c>
-      <c r="D25" s="11"/>
+      <c r="D25" s="7"/>
       <c r="E25" s="10">
         <f>IF(D25="","",EDATE(D25,36))</f>
       </c>
-      <c r="F25" s="11"/>
+      <c r="F25" s="7"/>
       <c r="G25" s="10">
         <f>IF(F25="","",EDATE(F25,12))</f>
       </c>
-      <c r="H25" s="11"/>
+      <c r="H25" s="7"/>
       <c r="I25" s="10">
         <f>IF(H25="","",EDATE(H25,12))</f>
       </c>
-      <c r="J25" s="11"/>
+      <c r="J25" s="7"/>
       <c r="K25" s="10">
         <f>IF(J25="","",EDATE(J25,36))</f>
       </c>
-      <c r="L25" s="11"/>
+      <c r="L25" s="7"/>
       <c r="M25" s="10">
         <f>IF(L25="","",EDATE(L25,12))</f>
       </c>
-      <c r="N25" s="11"/>
+      <c r="N25" s="7"/>
       <c r="O25" s="10">
         <f>IF(N25="","",EDATE(N25,12))</f>
       </c>
-      <c r="P25" s="11"/>
+      <c r="P25" s="7"/>
       <c r="Q25" s="10">
         <f>IF(P25="","",EDATE(P25,24))</f>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5"/>
-      <c r="B26" s="11"/>
+      <c r="B26" s="7"/>
       <c r="C26" s="10">
         <f>IF(B26="","",EDATE(B26,12))</f>
       </c>
-      <c r="D26" s="11"/>
+      <c r="D26" s="7"/>
       <c r="E26" s="10">
         <f>IF(D26="","",EDATE(D26,36))</f>
       </c>
-      <c r="F26" s="11"/>
+      <c r="F26" s="7"/>
       <c r="G26" s="10">
         <f>IF(F26="","",EDATE(F26,12))</f>
       </c>
-      <c r="H26" s="11"/>
+      <c r="H26" s="7"/>
       <c r="I26" s="10">
         <f>IF(H26="","",EDATE(H26,12))</f>
       </c>
-      <c r="J26" s="11"/>
+      <c r="J26" s="7"/>
       <c r="K26" s="10">
         <f>IF(J26="","",EDATE(J26,36))</f>
       </c>
-      <c r="L26" s="11"/>
+      <c r="L26" s="7"/>
       <c r="M26" s="10">
         <f>IF(L26="","",EDATE(L26,12))</f>
       </c>
-      <c r="N26" s="11"/>
+      <c r="N26" s="7"/>
       <c r="O26" s="10">
         <f>IF(N26="","",EDATE(N26,12))</f>
       </c>
-      <c r="P26" s="11"/>
+      <c r="P26" s="7"/>
       <c r="Q26" s="10">
         <f>IF(P26="","",EDATE(P26,24))</f>
       </c>
@@ -1364,7 +4608,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF0D5C45"/>
@@ -1427,236 +4671,236 @@
           <t>Example, overtype or delete me</t>
         </is>
       </c>
-      <c r="B5" s="11">
+      <c r="B5" s="7">
         <v>28</v>
       </c>
-      <c r="C5" s="9">
-        <v>46222</v>
-      </c>
-      <c r="D5" s="12">
+      <c r="C5" s="11">
+        <v>46231</v>
+      </c>
+      <c r="D5" s="9">
         <f>IF(C5="","",TODAY()-C5)</f>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="9">
         <f>IF(C5="","",IF(TODAY()-C5&gt;B5,"OVERDUE",IF(TODAY()-C5&gt;B5-7,"DUE","OK")))</f>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5"/>
-      <c r="B6" s="11"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="12">
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="9">
         <f>IF(C6="","",TODAY()-C6)</f>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="9">
         <f>IF(C6="","",IF(TODAY()-C6&gt;B6,"OVERDUE",IF(TODAY()-C6&gt;B6-7,"DUE","OK")))</f>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5"/>
-      <c r="B7" s="11"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="12">
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="9">
         <f>IF(C7="","",TODAY()-C7)</f>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="9">
         <f>IF(C7="","",IF(TODAY()-C7&gt;B7,"OVERDUE",IF(TODAY()-C7&gt;B7-7,"DUE","OK")))</f>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5"/>
-      <c r="B8" s="11"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="12">
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="9">
         <f>IF(C8="","",TODAY()-C8)</f>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="9">
         <f>IF(C8="","",IF(TODAY()-C8&gt;B8,"OVERDUE",IF(TODAY()-C8&gt;B8-7,"DUE","OK")))</f>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5"/>
-      <c r="B9" s="11"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="12">
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="9">
         <f>IF(C9="","",TODAY()-C9)</f>
       </c>
-      <c r="E9" s="12">
+      <c r="E9" s="9">
         <f>IF(C9="","",IF(TODAY()-C9&gt;B9,"OVERDUE",IF(TODAY()-C9&gt;B9-7,"DUE","OK")))</f>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5"/>
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="12">
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="9">
         <f>IF(C10="","",TODAY()-C10)</f>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="9">
         <f>IF(C10="","",IF(TODAY()-C10&gt;B10,"OVERDUE",IF(TODAY()-C10&gt;B10-7,"DUE","OK")))</f>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="12">
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="9">
         <f>IF(C11="","",TODAY()-C11)</f>
       </c>
-      <c r="E11" s="12">
+      <c r="E11" s="9">
         <f>IF(C11="","",IF(TODAY()-C11&gt;B11,"OVERDUE",IF(TODAY()-C11&gt;B11-7,"DUE","OK")))</f>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="12">
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="9">
         <f>IF(C12="","",TODAY()-C12)</f>
       </c>
-      <c r="E12" s="12">
+      <c r="E12" s="9">
         <f>IF(C12="","",IF(TODAY()-C12&gt;B12,"OVERDUE",IF(TODAY()-C12&gt;B12-7,"DUE","OK")))</f>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="12">
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="9">
         <f>IF(C13="","",TODAY()-C13)</f>
       </c>
-      <c r="E13" s="12">
+      <c r="E13" s="9">
         <f>IF(C13="","",IF(TODAY()-C13&gt;B13,"OVERDUE",IF(TODAY()-C13&gt;B13-7,"DUE","OK")))</f>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="12">
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="9">
         <f>IF(C14="","",TODAY()-C14)</f>
       </c>
-      <c r="E14" s="12">
+      <c r="E14" s="9">
         <f>IF(C14="","",IF(TODAY()-C14&gt;B14,"OVERDUE",IF(TODAY()-C14&gt;B14-7,"DUE","OK")))</f>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5"/>
-      <c r="B15" s="11"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="12">
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="9">
         <f>IF(C15="","",TODAY()-C15)</f>
       </c>
-      <c r="E15" s="12">
+      <c r="E15" s="9">
         <f>IF(C15="","",IF(TODAY()-C15&gt;B15,"OVERDUE",IF(TODAY()-C15&gt;B15-7,"DUE","OK")))</f>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5"/>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="12">
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="9">
         <f>IF(C16="","",TODAY()-C16)</f>
       </c>
-      <c r="E16" s="12">
+      <c r="E16" s="9">
         <f>IF(C16="","",IF(TODAY()-C16&gt;B16,"OVERDUE",IF(TODAY()-C16&gt;B16-7,"DUE","OK")))</f>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5"/>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="12">
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="9">
         <f>IF(C17="","",TODAY()-C17)</f>
       </c>
-      <c r="E17" s="12">
+      <c r="E17" s="9">
         <f>IF(C17="","",IF(TODAY()-C17&gt;B17,"OVERDUE",IF(TODAY()-C17&gt;B17-7,"DUE","OK")))</f>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5"/>
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="12">
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="9">
         <f>IF(C18="","",TODAY()-C18)</f>
       </c>
-      <c r="E18" s="12">
+      <c r="E18" s="9">
         <f>IF(C18="","",IF(TODAY()-C18&gt;B18,"OVERDUE",IF(TODAY()-C18&gt;B18-7,"DUE","OK")))</f>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5"/>
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="12">
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="9">
         <f>IF(C19="","",TODAY()-C19)</f>
       </c>
-      <c r="E19" s="12">
+      <c r="E19" s="9">
         <f>IF(C19="","",IF(TODAY()-C19&gt;B19,"OVERDUE",IF(TODAY()-C19&gt;B19-7,"DUE","OK")))</f>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5"/>
-      <c r="B20" s="11"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="12">
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="9">
         <f>IF(C20="","",TODAY()-C20)</f>
       </c>
-      <c r="E20" s="12">
+      <c r="E20" s="9">
         <f>IF(C20="","",IF(TODAY()-C20&gt;B20,"OVERDUE",IF(TODAY()-C20&gt;B20-7,"DUE","OK")))</f>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5"/>
-      <c r="B21" s="11"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="12">
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="9">
         <f>IF(C21="","",TODAY()-C21)</f>
       </c>
-      <c r="E21" s="12">
+      <c r="E21" s="9">
         <f>IF(C21="","",IF(TODAY()-C21&gt;B21,"OVERDUE",IF(TODAY()-C21&gt;B21-7,"DUE","OK")))</f>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5"/>
-      <c r="B22" s="11"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="12">
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="9">
         <f>IF(C22="","",TODAY()-C22)</f>
       </c>
-      <c r="E22" s="12">
+      <c r="E22" s="9">
         <f>IF(C22="","",IF(TODAY()-C22&gt;B22,"OVERDUE",IF(TODAY()-C22&gt;B22-7,"DUE","OK")))</f>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5"/>
-      <c r="B23" s="11"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="12">
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="9">
         <f>IF(C23="","",TODAY()-C23)</f>
       </c>
-      <c r="E23" s="12">
+      <c r="E23" s="9">
         <f>IF(C23="","",IF(TODAY()-C23&gt;B23,"OVERDUE",IF(TODAY()-C23&gt;B23-7,"DUE","OK")))</f>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5"/>
-      <c r="B24" s="11"/>
-      <c r="C24" s="11"/>
-      <c r="D24" s="12">
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="9">
         <f>IF(C24="","",TODAY()-C24)</f>
       </c>
-      <c r="E24" s="12">
+      <c r="E24" s="9">
         <f>IF(C24="","",IF(TODAY()-C24&gt;B24,"OVERDUE",IF(TODAY()-C24&gt;B24-7,"DUE","OK")))</f>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5"/>
-      <c r="B25" s="11"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="12">
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="9">
         <f>IF(C25="","",TODAY()-C25)</f>
       </c>
-      <c r="E25" s="12">
+      <c r="E25" s="9">
         <f>IF(C25="","",IF(TODAY()-C25&gt;B25,"OVERDUE",IF(TODAY()-C25&gt;B25-7,"DUE","OK")))</f>
       </c>
     </row>
@@ -1681,7 +4925,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF0D5C45"/>
@@ -1707,7 +4951,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>For staff on the Update Service: run the status check twice a year (one minute each, with consent) and note the date. Next due computes itself.</t>
+          <t>For staff on the Update Service: there is no set frequency in the regulations, and a common policy is a status check every six months (one minute each, with consent). Note the date and the next one computes itself.</t>
         </is>
       </c>
     </row>
@@ -1755,13 +4999,13 @@
           <t>001234567890</t>
         </is>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D5" s="9">
-        <v>46061</v>
+      <c r="D5" s="11">
+        <v>46071</v>
       </c>
       <c r="E5" s="10">
         <f>IF(D5="","",EDATE(D5,6))</f>
@@ -1775,8 +5019,8 @@
     <row r="6">
       <c r="A6" s="5"/>
       <c r="B6" s="5"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
       <c r="E6" s="10">
         <f>IF(D6="","",EDATE(D6,6))</f>
       </c>
@@ -1785,8 +5029,8 @@
     <row r="7">
       <c r="A7" s="5"/>
       <c r="B7" s="5"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
       <c r="E7" s="10">
         <f>IF(D7="","",EDATE(D7,6))</f>
       </c>
@@ -1795,8 +5039,8 @@
     <row r="8">
       <c r="A8" s="5"/>
       <c r="B8" s="5"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
       <c r="E8" s="10">
         <f>IF(D8="","",EDATE(D8,6))</f>
       </c>
@@ -1805,8 +5049,8 @@
     <row r="9">
       <c r="A9" s="5"/>
       <c r="B9" s="5"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
       <c r="E9" s="10">
         <f>IF(D9="","",EDATE(D9,6))</f>
       </c>
@@ -1815,8 +5059,8 @@
     <row r="10">
       <c r="A10" s="5"/>
       <c r="B10" s="5"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
       <c r="E10" s="10">
         <f>IF(D10="","",EDATE(D10,6))</f>
       </c>
@@ -1825,8 +5069,8 @@
     <row r="11">
       <c r="A11" s="5"/>
       <c r="B11" s="5"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
       <c r="E11" s="10">
         <f>IF(D11="","",EDATE(D11,6))</f>
       </c>
@@ -1835,8 +5079,8 @@
     <row r="12">
       <c r="A12" s="5"/>
       <c r="B12" s="5"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
       <c r="E12" s="10">
         <f>IF(D12="","",EDATE(D12,6))</f>
       </c>
@@ -1845,8 +5089,8 @@
     <row r="13">
       <c r="A13" s="5"/>
       <c r="B13" s="5"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
       <c r="E13" s="10">
         <f>IF(D13="","",EDATE(D13,6))</f>
       </c>
@@ -1855,8 +5099,8 @@
     <row r="14">
       <c r="A14" s="5"/>
       <c r="B14" s="5"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
       <c r="E14" s="10">
         <f>IF(D14="","",EDATE(D14,6))</f>
       </c>
@@ -1865,8 +5109,8 @@
     <row r="15">
       <c r="A15" s="5"/>
       <c r="B15" s="5"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
       <c r="E15" s="10">
         <f>IF(D15="","",EDATE(D15,6))</f>
       </c>
@@ -1875,8 +5119,8 @@
     <row r="16">
       <c r="A16" s="5"/>
       <c r="B16" s="5"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
       <c r="E16" s="10">
         <f>IF(D16="","",EDATE(D16,6))</f>
       </c>
@@ -1885,8 +5129,8 @@
     <row r="17">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
       <c r="E17" s="10">
         <f>IF(D17="","",EDATE(D17,6))</f>
       </c>
@@ -1895,8 +5139,8 @@
     <row r="18">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
       <c r="E18" s="10">
         <f>IF(D18="","",EDATE(D18,6))</f>
       </c>
@@ -1905,8 +5149,8 @@
     <row r="19">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
       <c r="E19" s="10">
         <f>IF(D19="","",EDATE(D19,6))</f>
       </c>
@@ -1915,8 +5159,8 @@
     <row r="20">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
       <c r="E20" s="10">
         <f>IF(D20="","",EDATE(D20,6))</f>
       </c>
@@ -1925,8 +5169,8 @@
     <row r="21">
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
       <c r="E21" s="10">
         <f>IF(D21="","",EDATE(D21,6))</f>
       </c>
@@ -1935,8 +5179,8 @@
     <row r="22">
       <c r="A22" s="5"/>
       <c r="B22" s="5"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
       <c r="E22" s="10">
         <f>IF(D22="","",EDATE(D22,6))</f>
       </c>
@@ -1945,8 +5189,8 @@
     <row r="23">
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
       <c r="E23" s="10">
         <f>IF(D23="","",EDATE(D23,6))</f>
       </c>
@@ -1955,8 +5199,8 @@
     <row r="24">
       <c r="A24" s="5"/>
       <c r="B24" s="5"/>
-      <c r="C24" s="11"/>
-      <c r="D24" s="11"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
       <c r="E24" s="10">
         <f>IF(D24="","",EDATE(D24,6))</f>
       </c>
@@ -1965,8 +5209,8 @@
     <row r="25">
       <c r="A25" s="5"/>
       <c r="B25" s="5"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="11"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
       <c r="E25" s="10">
         <f>IF(D25="","",EDATE(D25,6))</f>
       </c>
@@ -1993,257 +5237,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="FF0D5C45"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="26" customWidth="1"/>
-    <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="15" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Diploma clocks</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Care staff must gain the Level 3 Diploma within two years of starting. Start date plus Yes or No; the deadline computes itself.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>Staff member</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Start date</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Holds Level 3? (Yes/No)</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Level 3 due by</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>Example, overtype or delete me</t>
-        </is>
-      </c>
-      <c r="B5" s="9">
-        <v>45762</v>
-      </c>
-      <c r="C5" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D5" s="10">
-        <f>IF(OR(B5="",C5="Yes"),"",EDATE(B5,24))</f>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5"/>
-      <c r="B6" s="11"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="10">
-        <f>IF(OR(B6="",C6="Yes"),"",EDATE(B6,24))</f>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5"/>
-      <c r="B7" s="11"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="10">
-        <f>IF(OR(B7="",C7="Yes"),"",EDATE(B7,24))</f>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5"/>
-      <c r="B8" s="11"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="10">
-        <f>IF(OR(B8="",C8="Yes"),"",EDATE(B8,24))</f>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5"/>
-      <c r="B9" s="11"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="10">
-        <f>IF(OR(B9="",C9="Yes"),"",EDATE(B9,24))</f>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5"/>
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="10">
-        <f>IF(OR(B10="",C10="Yes"),"",EDATE(B10,24))</f>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="10">
-        <f>IF(OR(B11="",C11="Yes"),"",EDATE(B11,24))</f>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="10">
-        <f>IF(OR(B12="",C12="Yes"),"",EDATE(B12,24))</f>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="10">
-        <f>IF(OR(B13="",C13="Yes"),"",EDATE(B13,24))</f>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="10">
-        <f>IF(OR(B14="",C14="Yes"),"",EDATE(B14,24))</f>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5"/>
-      <c r="B15" s="11"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="10">
-        <f>IF(OR(B15="",C15="Yes"),"",EDATE(B15,24))</f>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5"/>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="10">
-        <f>IF(OR(B16="",C16="Yes"),"",EDATE(B16,24))</f>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5"/>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="10">
-        <f>IF(OR(B17="",C17="Yes"),"",EDATE(B17,24))</f>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5"/>
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="10">
-        <f>IF(OR(B18="",C18="Yes"),"",EDATE(B18,24))</f>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5"/>
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="10">
-        <f>IF(OR(B19="",C19="Yes"),"",EDATE(B19,24))</f>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5"/>
-      <c r="B20" s="11"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="10">
-        <f>IF(OR(B20="",C20="Yes"),"",EDATE(B20,24))</f>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5"/>
-      <c r="B21" s="11"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="10">
-        <f>IF(OR(B21="",C21="Yes"),"",EDATE(B21,24))</f>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5"/>
-      <c r="B22" s="11"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="10">
-        <f>IF(OR(B22="",C22="Yes"),"",EDATE(B22,24))</f>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5"/>
-      <c r="B23" s="11"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="10">
-        <f>IF(OR(B23="",C23="Yes"),"",EDATE(B23,24))</f>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5"/>
-      <c r="B24" s="11"/>
-      <c r="C24" s="11"/>
-      <c r="D24" s="10">
-        <f>IF(OR(B24="",C24="Yes"),"",EDATE(B24,24))</f>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5"/>
-      <c r="B25" s="11"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="10">
-        <f>IF(OR(B25="",C25="Yes"),"",EDATE(B25,24))</f>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:D2"/>
-  </mergeCells>
-  <conditionalFormatting sqref="D5:D25">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>AND(D5&lt;&gt;"",D5&lt;TODAY())</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>AND(D5&lt;&gt;"",D5&lt;TODAY()+90)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="2" priority="3">
-      <formula>AND(D5&lt;&gt;"",D5&gt;=TODAY()+90)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF0D5C45"/>
@@ -2300,8 +5294,8 @@
           <t>Statement of purpose</t>
         </is>
       </c>
-      <c r="B5" s="11"/>
-      <c r="C5" s="11">
+      <c r="B5" s="7"/>
+      <c r="C5" s="7">
         <v>12</v>
       </c>
       <c r="D5" s="10">
@@ -2314,8 +5308,8 @@
           <t>Location risk assessment</t>
         </is>
       </c>
-      <c r="B6" s="11"/>
-      <c r="C6" s="11">
+      <c r="B6" s="7"/>
+      <c r="C6" s="7">
         <v>12</v>
       </c>
       <c r="D6" s="10">
@@ -2328,8 +5322,8 @@
           <t>Safeguarding policy</t>
         </is>
       </c>
-      <c r="B7" s="11"/>
-      <c r="C7" s="11">
+      <c r="B7" s="7"/>
+      <c r="C7" s="7">
         <v>12</v>
       </c>
       <c r="D7" s="10">
@@ -2342,8 +5336,8 @@
           <t>Behaviour support policy</t>
         </is>
       </c>
-      <c r="B8" s="11"/>
-      <c r="C8" s="11">
+      <c r="B8" s="7"/>
+      <c r="C8" s="7">
         <v>12</v>
       </c>
       <c r="D8" s="10">
@@ -2356,8 +5350,8 @@
           <t>Missing child policy</t>
         </is>
       </c>
-      <c r="B9" s="11"/>
-      <c r="C9" s="11">
+      <c r="B9" s="7"/>
+      <c r="C9" s="7">
         <v>12</v>
       </c>
       <c r="D9" s="10">
@@ -2370,8 +5364,8 @@
           <t>Complaints policy</t>
         </is>
       </c>
-      <c r="B10" s="11"/>
-      <c r="C10" s="11">
+      <c r="B10" s="7"/>
+      <c r="C10" s="7">
         <v>12</v>
       </c>
       <c r="D10" s="10">
@@ -2384,8 +5378,8 @@
           <t>Lone working assessment</t>
         </is>
       </c>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11">
+      <c r="B11" s="7"/>
+      <c r="C11" s="7">
         <v>12</v>
       </c>
       <c r="D11" s="10">
@@ -2398,8 +5392,8 @@
           <t>Workforce plan</t>
         </is>
       </c>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11">
+      <c r="B12" s="7"/>
+      <c r="C12" s="7">
         <v>12</v>
       </c>
       <c r="D12" s="10">
@@ -2442,9 +5436,9 @@
           <t>January</t>
         </is>
       </c>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -2452,9 +5446,9 @@
           <t>February</t>
         </is>
       </c>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -2462,9 +5456,9 @@
           <t>March</t>
         </is>
       </c>
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -2472,9 +5466,9 @@
           <t>April</t>
         </is>
       </c>
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -2482,9 +5476,9 @@
           <t>May</t>
         </is>
       </c>
-      <c r="B20" s="11"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -2492,9 +5486,9 @@
           <t>June</t>
         </is>
       </c>
-      <c r="B21" s="11"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -2502,9 +5496,9 @@
           <t>July</t>
         </is>
       </c>
-      <c r="B22" s="11"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -2512,9 +5506,9 @@
           <t>August</t>
         </is>
       </c>
-      <c r="B23" s="11"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -2522,9 +5516,9 @@
           <t>September</t>
         </is>
       </c>
-      <c r="B24" s="11"/>
-      <c r="C24" s="11"/>
-      <c r="D24" s="11"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -2532,9 +5526,9 @@
           <t>October</t>
         </is>
       </c>
-      <c r="B25" s="11"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="11"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -2542,9 +5536,9 @@
           <t>November</t>
         </is>
       </c>
-      <c r="B26" s="11"/>
-      <c r="C26" s="11"/>
-      <c r="D26" s="11"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -2552,9 +5546,9 @@
           <t>December</t>
         </is>
       </c>
-      <c r="B27" s="11"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="11"/>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
     </row>
     <row r="28"/>
     <row r="29">
@@ -2585,7 +5579,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF0D5C45"/>
@@ -2653,8 +5647,8 @@
           <t>Passport or licence plus a dated photo, copies in the file</t>
         </is>
       </c>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
       <c r="E5" s="5"/>
     </row>
     <row r="6">
@@ -2668,8 +5662,8 @@
           <t>Certificate number and date recorded; never the disclosure content</t>
         </is>
       </c>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
       <c r="E6" s="5"/>
     </row>
     <row r="7">
@@ -2683,8 +5677,8 @@
           <t>On file, checked by phone, with a note of the call</t>
         </is>
       </c>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
       <c r="E7" s="5"/>
     </row>
     <row r="8">
@@ -2698,8 +5692,8 @@
           <t>Checked as far as practicable, in writing</t>
         </is>
       </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
       <c r="E8" s="5"/>
     </row>
     <row r="9">
@@ -2713,8 +5707,8 @@
           <t>The certificates themselves, not a CV line</t>
         </is>
       </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
       <c r="E9" s="5"/>
     </row>
     <row r="10">
@@ -2728,8 +5722,8 @@
           <t>Use the Employment gaps tab; anything over a month needs a sentence</t>
         </is>
       </c>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
       <c r="E10" s="5"/>
     </row>
     <row r="11">
@@ -2743,8 +5737,8 @@
           <t>Evidence checked and copied before day one</t>
         </is>
       </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
       <c r="E11" s="5"/>
     </row>
     <row r="12">
@@ -2758,8 +5752,8 @@
           <t>Assessment date recorded; the assessment itself stays with occupational health</t>
         </is>
       </c>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
       <c r="E12" s="5"/>
     </row>
     <row r="13">
@@ -2773,8 +5767,8 @@
           <t>Who interviewed, when, and the judgment reached</t>
         </is>
       </c>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
       <c r="E13" s="5"/>
     </row>
     <row r="14">
@@ -2788,8 +5782,8 @@
           <t>Consent noted and the date of the last status check</t>
         </is>
       </c>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
       <c r="E14" s="5"/>
     </row>
   </sheetData>
@@ -2800,368 +5794,4 @@
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="FF0D5C45"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="36" customWidth="1"/>
-    <col min="4" max="4" width="24" customWidth="1"/>
-    <col min="5" max="5" width="26" customWidth="1"/>
-    <col min="6" max="6" width="10" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Employment history, gaps explained</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Work backwards from their current job. The most common file failure is a gap with no written explanation. "Travelling" written down is a pass. Silence is a finding.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>From (month/year)</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>To (month/year)</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Employer, course, or what the gap was</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Role</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>Reason for leaving</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>Checked?</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="11"/>
-      <c r="B5" s="11"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="11"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="11"/>
-      <c r="B6" s="11"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="11"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="11"/>
-      <c r="B7" s="11"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="11"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="11"/>
-      <c r="B8" s="11"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="11"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="11"/>
-      <c r="B9" s="11"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="11"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="11"/>
-      <c r="B10" s="11"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="11"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="11"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="11"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="11"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="11"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="11"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="11"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="11"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="11"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="11"/>
-      <c r="B15" s="11"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="11"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="11"/>
-      <c r="B16" s="11"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="11"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="11"/>
-      <c r="B17" s="11"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="11"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="11"/>
-      <c r="B18" s="11"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="11"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="11"/>
-      <c r="B19" s="11"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="11"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:F2"/>
-  </mergeCells>
-  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="FF0D5C45"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="46" customWidth="1"/>
-    <col min="2" max="2" width="30" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="40" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>The inspector's opening list</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>The eleven staff-side things every full inspection asks for. Grade yourself honestly before Ofsted does it for you.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>The inspector asks for</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Where yours lives today</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Ready / Question / Gap</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>What would make it Ready</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Statement of purpose, current and reviewed</t>
-        </is>
-      </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="5"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Staff list with qualifications and planned qualification updates</t>
-        </is>
-      </c>
-      <c r="B6" s="5"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="5"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Recruitment and vetting records, complete for every person</t>
-        </is>
-      </c>
-      <c r="B7" s="5"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="5"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>Training records, mandatory courses in date</t>
-        </is>
-      </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="5"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Supervision records, everyone in cycle including the manager</t>
-        </is>
-      </c>
-      <c r="B9" s="5"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="5"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>Staffing rotas, planned and as actually worked</t>
-        </is>
-      </c>
-      <c r="B10" s="5"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="5"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>Allegations records, held securely with timescales evidenced</t>
-        </is>
-      </c>
-      <c r="B11" s="5"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="5"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>Reports of monthly regulation 44 visits</t>
-        </is>
-      </c>
-      <c r="B12" s="5"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="5"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Regulation 45 quality of care report, within six months</t>
-        </is>
-      </c>
-      <c r="B13" s="5"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="5"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>Notifications made to Ofsted, with who else was told</t>
-        </is>
-      </c>
-      <c r="B14" s="5"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="5"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>Location assessment, reviewed within the year</t>
-        </is>
-      </c>
-      <c r="B15" s="5"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="5"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:D2"/>
-  </mergeCells>
-  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
-</worksheet>
 </file>